--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.499492372684</v>
+        <v>46073.66615903935</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55752832176</v>
+        <v>46092.72419498843</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.363893738424</v>
+        <v>46097.530560405095</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1613,13 +1613,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.499492731484</v>
+        <v>46073.66615939815</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55750113426</v>
+        <v>46092.72416780093</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71140298611</v>
+        <v>46133.87806965278</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1678,13 +1678,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.49949296296</v>
+        <v>46073.66615962963</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55750163195</v>
+        <v>46092.724168298606</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55752931713</v>
+        <v>46092.7241959838</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1743,13 +1743,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.49949321759</v>
+        <v>46073.66615988426</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55750206018</v>
+        <v>46092.724168726854</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55752958333</v>
+        <v>46092.72419625</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1808,13 +1808,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.499493564814</v>
+        <v>46073.666160231485</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55750253472</v>
+        <v>46092.72416920139</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.598443587965</v>
+        <v>46100.76511025463</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1873,13 +1873,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.499493807874</v>
+        <v>46073.66616047454</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.557503159725</v>
+        <v>46092.72416982639</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55752962963</v>
+        <v>46092.7241962963</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1938,13 +1938,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.49949412037</v>
+        <v>46073.666160787034</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.43689293982</v>
+        <v>46129.60355960648</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.43690697917</v>
+        <v>46129.60357364583</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1991,13 +1991,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.499494386575</v>
+        <v>46073.66616105324</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.36529939815</v>
+        <v>46097.53196606482</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.36531625</v>
+        <v>46097.53198291667</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2056,13 +2056,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.49949462963</v>
+        <v>46073.66616129629</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.436877581014</v>
+        <v>46129.603544247686</v>
       </c>
       <c r="D12" s="5">
-        <v>46129.43715770834</v>
+        <v>46129.603824375</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2121,13 +2121,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.499494930555</v>
+        <v>46073.666161597226</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.36376251157</v>
+        <v>46097.53042917824</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.60747927084</v>
+        <v>46129.774145937496</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2170,13 +2170,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.49949347222</v>
+        <v>46073.66616013889</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.361171655095</v>
+        <v>46097.52783832176</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.36119037037</v>
+        <v>46097.527857037036</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2235,13 +2235,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.49949430556</v>
+        <v>46073.66616097222</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.36364943287</v>
+        <v>46097.53031609954</v>
       </c>
       <c r="D15" s="8">
-        <v>46100.59837325232</v>
+        <v>46100.76503991898</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2300,13 +2300,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.49949460648</v>
+        <v>46073.66616127315</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.36153350695</v>
+        <v>46097.52820017361</v>
       </c>
       <c r="D16" s="5">
-        <v>46100.59906158565</v>
+        <v>46100.765728252314</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2365,13 +2365,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.4994949074</v>
+        <v>46073.666161574074</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.3637440162</v>
+        <v>46097.53041068287</v>
       </c>
       <c r="D17" s="8">
-        <v>46133.463954363426</v>
+        <v>46133.6306210301</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2430,13 +2430,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.499495208336</v>
+        <v>46073.666161875</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.63087541667</v>
+        <v>46107.79754208333</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.46406146991</v>
+        <v>46133.63072813657</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2479,13 +2479,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.49949577547</v>
+        <v>46073.666162442125</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.36397681713</v>
+        <v>46097.5306434838</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.363992812505</v>
+        <v>46097.53065947916</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2544,13 +2544,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.49949549769</v>
+        <v>46073.66616216435</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.36402971065</v>
+        <v>46097.53069637732</v>
       </c>
       <c r="D20" s="5">
-        <v>46133.464000300926</v>
+        <v>46133.6306669676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2609,13 +2609,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.49949605324</v>
+        <v>46073.66616271991</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.36537702546</v>
+        <v>46097.53204369213</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.36539537037</v>
+        <v>46097.53206203703</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2674,13 +2674,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.49949634259</v>
+        <v>46073.66616300926</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.364136944445</v>
+        <v>46097.53080361111</v>
       </c>
       <c r="D22" s="5">
-        <v>46100.5974815625</v>
+        <v>46100.764148229166</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2739,13 +2739,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.49949341435</v>
+        <v>46073.66616008102</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.36407888889</v>
+        <v>46097.53074555556</v>
       </c>
       <c r="D23" s="8">
-        <v>46100.59760299769</v>
+        <v>46100.76426966435</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2804,13 +2804,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46076.496493715276</v>
+        <v>46076.66316038194</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.63085673611</v>
+        <v>46107.797523402776</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.63087702546</v>
+        <v>46107.797543692126</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2869,13 +2869,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46099.366391400465</v>
+        <v>46099.53305806713</v>
       </c>
       <c r="C25" s="8">
-        <v>46099.36740725694</v>
+        <v>46099.53407392361</v>
       </c>
       <c r="D25" s="8">
-        <v>46133.463979629625</v>
+        <v>46133.6306462963</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2934,13 +2934,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.49949376157</v>
+        <v>46073.66616042824</v>
       </c>
       <c r="C26" s="5">
-        <v>46120.539350046296</v>
+        <v>46120.70601671297</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.46416554398</v>
+        <v>46133.63083221065</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2983,13 +2983,13 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.499494641204</v>
+        <v>46073.66616130787</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.633942430555</v>
+        <v>46107.80060909722</v>
       </c>
       <c r="D27" s="8">
-        <v>46133.46411260417</v>
+        <v>46133.63077927083</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -3048,13 +3048,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.49949495371</v>
+        <v>46073.66616162037</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.36473247685</v>
+        <v>46097.53139914352</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.364734305556</v>
+        <v>46097.53140097222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3109,13 +3109,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.4994953125</v>
+        <v>46073.66616197917</v>
       </c>
       <c r="C29" s="8">
-        <v>46107.63388674769</v>
+        <v>46107.80055341435</v>
       </c>
       <c r="D29" s="8">
-        <v>46107.63388792824</v>
+        <v>46107.80055459491</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3170,13 +3170,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.499495682874</v>
+        <v>46073.66616234954</v>
       </c>
       <c r="C30" s="5">
-        <v>46107.63392649306</v>
+        <v>46107.80059315972</v>
       </c>
       <c r="D30" s="5">
-        <v>46107.63392796296</v>
+        <v>46107.80059462963</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3231,13 +3231,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.4994940162</v>
+        <v>46073.66616068287</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.3646569213</v>
+        <v>46097.53132358796</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.36466953704</v>
+        <v>46097.531336203705</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3296,13 +3296,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.49949431713</v>
+        <v>46073.6661609838</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.3646059375</v>
+        <v>46097.53127260417</v>
       </c>
       <c r="D32" s="5">
-        <v>46099.36713922454</v>
+        <v>46099.5338058912</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3357,13 +3357,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.49949459491</v>
+        <v>46073.66616126157</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.36464347222</v>
+        <v>46097.53131013889</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.36464501158</v>
+        <v>46097.53131167824</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3418,13 +3418,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.49949484954</v>
+        <v>46073.6661615162</v>
       </c>
       <c r="C34" s="5">
-        <v>46120.50183533565</v>
+        <v>46120.668502002314</v>
       </c>
       <c r="D34" s="5">
-        <v>46120.50184832176</v>
+        <v>46120.66851498843</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3483,13 +3483,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.49949511574</v>
+        <v>46073.66616178241</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.36541935185</v>
+        <v>46097.53208601852</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.36542087963</v>
+        <v>46097.53208754629</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3544,13 +3544,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.499495393524</v>
+        <v>46073.66616206018</v>
       </c>
       <c r="C36" s="5">
-        <v>46120.50182016204</v>
+        <v>46120.668486828705</v>
       </c>
       <c r="D36" s="5">
-        <v>46120.5018218287</v>
+        <v>46120.66848849537</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3605,13 +3605,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.49949565972</v>
+        <v>46073.66616232639</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.63205829861</v>
+        <v>46107.79872496528</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.63207070602</v>
+        <v>46107.79873737269</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3670,13 +3670,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.4994959375</v>
+        <v>46073.66616260417</v>
       </c>
       <c r="C38" s="5">
-        <v>46107.63195207176</v>
+        <v>46107.79861873842</v>
       </c>
       <c r="D38" s="5">
-        <v>46107.63195350695</v>
+        <v>46107.798620173606</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3731,13 +3731,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.49949421296</v>
+        <v>46073.66616087963</v>
       </c>
       <c r="C39" s="8">
-        <v>46107.6320437963</v>
+        <v>46107.798710462965</v>
       </c>
       <c r="D39" s="8">
-        <v>46107.63204511574</v>
+        <v>46107.79871178241</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3792,13 +3792,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.499496018514</v>
+        <v>46073.666162685186</v>
       </c>
       <c r="C40" s="5">
-        <v>46098.51516494213</v>
+        <v>46098.681831608796</v>
       </c>
       <c r="D40" s="5">
-        <v>46098.51535857639</v>
+        <v>46098.682025243055</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3857,13 +3857,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.49949633102</v>
+        <v>46073.66616299769</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.36488233796</v>
+        <v>46097.531549004634</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.36488371528</v>
+        <v>46097.531550381944</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3918,13 +3918,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.49949665509</v>
+        <v>46073.66616332176</v>
       </c>
       <c r="C42" s="5">
-        <v>46098.51514953704</v>
+        <v>46098.68181620371</v>
       </c>
       <c r="D42" s="5">
-        <v>46098.51515129629</v>
+        <v>46098.68181796296</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3979,13 +3979,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.514133715275</v>
+        <v>46076.680800381946</v>
       </c>
       <c r="C43" s="8">
-        <v>46107.63418584491</v>
+        <v>46107.80085251157</v>
       </c>
       <c r="D43" s="8">
-        <v>46107.634225173606</v>
+        <v>46107.80089184028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4044,13 +4044,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.51685321759</v>
+        <v>46076.68351988426</v>
       </c>
       <c r="C44" s="5">
-        <v>46107.63219305556</v>
+        <v>46107.79885972222</v>
       </c>
       <c r="D44" s="5">
-        <v>46107.632194861115</v>
+        <v>46107.79886152778</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4109,13 +4109,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46076.5170812037</v>
+        <v>46076.68374787037</v>
       </c>
       <c r="C45" s="8">
-        <v>46107.634169467594</v>
+        <v>46107.80083613426</v>
       </c>
       <c r="D45" s="8">
-        <v>46107.63417105324</v>
+        <v>46107.80083771991</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4174,13 +4174,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46099.36346302083</v>
+        <v>46099.5301296875</v>
       </c>
       <c r="C46" s="5">
-        <v>46120.4972005787</v>
+        <v>46120.66386724537</v>
       </c>
       <c r="D46" s="5">
-        <v>46133.46426173611</v>
+        <v>46133.63092840278</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4239,13 +4239,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="8">
-        <v>46099.36377777778</v>
+        <v>46099.53044444445</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.63450909722</v>
+        <v>46107.80117576389</v>
       </c>
       <c r="D47" s="8">
-        <v>46107.63451070602</v>
+        <v>46107.80117737269</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>101</v>
@@ -4294,13 +4294,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46099.36391869213</v>
+        <v>46099.53058535879</v>
       </c>
       <c r="C48" s="5">
-        <v>46120.49764869213</v>
+        <v>46120.664315358794</v>
       </c>
       <c r="D48" s="5">
-        <v>46120.49765023148</v>
+        <v>46120.664316898146</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>169</v>
@@ -4349,13 +4349,13 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46099.68312449074</v>
+        <v>46099.84979115741</v>
       </c>
       <c r="C49" s="8">
-        <v>46105.58778537037</v>
+        <v>46105.754452037036</v>
       </c>
       <c r="D49" s="8">
-        <v>46120.475501030094</v>
+        <v>46120.64216769676</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4404,13 +4404,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46099.683179837964</v>
+        <v>46099.84984650463</v>
       </c>
       <c r="C50" s="5">
-        <v>46120.49795726852</v>
+        <v>46120.66462393518</v>
       </c>
       <c r="D50" s="5">
-        <v>46120.49795851852</v>
+        <v>46120.664625185185</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4459,13 +4459,13 @@
         <v>181</v>
       </c>
       <c r="B51" s="8">
-        <v>46099.683643703705</v>
+        <v>46099.85031037037</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.497969131946</v>
+        <v>46120.66463579861</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.497970219905</v>
+        <v>46120.66463688658</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -4514,13 +4514,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46099.364613391204</v>
+        <v>46099.53128005787</v>
       </c>
       <c r="C52" s="5">
-        <v>46120.47419332176</v>
+        <v>46120.64085998843</v>
       </c>
       <c r="D52" s="5">
-        <v>46120.497655694446</v>
+        <v>46120.66432236111</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>185</v>
@@ -4569,13 +4569,13 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.49949696759</v>
+        <v>46073.66616363426</v>
       </c>
       <c r="C53" s="8">
-        <v>46171.53434295139</v>
+        <v>46171.70100961806</v>
       </c>
       <c r="D53" s="8">
-        <v>46171.53435428241</v>
+        <v>46171.70102094907</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>189</v>
@@ -4622,13 +4622,13 @@
         <v>191</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.499497337965</v>
+        <v>46073.66616400463</v>
       </c>
       <c r="C54" s="5">
-        <v>46098.35444456019</v>
+        <v>46098.52111122685</v>
       </c>
       <c r="D54" s="5">
-        <v>46098.3544667824</v>
+        <v>46098.521133449074</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -4687,13 +4687,13 @@
         <v>196</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.49949548611</v>
+        <v>46073.666162152775</v>
       </c>
       <c r="C55" s="8">
-        <v>46114.62113092592</v>
+        <v>46114.787797592595</v>
       </c>
       <c r="D55" s="8">
-        <v>46114.621132534725</v>
+        <v>46114.78779920139</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>197</v>
@@ -4752,13 +4752,13 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46091.50057788195</v>
+        <v>46091.66724454861</v>
       </c>
       <c r="C56" s="5">
-        <v>46114.62123172454</v>
+        <v>46114.78789839121</v>
       </c>
       <c r="D56" s="5">
-        <v>46114.62124690972</v>
+        <v>46114.787913576394</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4817,13 +4817,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46091.500609560186</v>
+        <v>46091.66727622686</v>
       </c>
       <c r="C57" s="8">
-        <v>46171.53432277778</v>
+        <v>46171.70098944445</v>
       </c>
       <c r="D57" s="8">
-        <v>46171.53434356481</v>
+        <v>46171.70101023148</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>204</v>
@@ -4882,13 +4882,13 @@
         <v>209</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.49949594907</v>
+        <v>46073.666162615744</v>
       </c>
       <c r="C58" s="5">
-        <v>46105.53177052083</v>
+        <v>46105.6984371875</v>
       </c>
       <c r="D58" s="5">
-        <v>46105.53178506944</v>
+        <v>46105.69845173611</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>210</v>
@@ -4935,13 +4935,13 @@
         <v>212</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.499496516204</v>
+        <v>46073.666163182876</v>
       </c>
       <c r="C59" s="8">
-        <v>46098.51852486111</v>
+        <v>46098.68519152778</v>
       </c>
       <c r="D59" s="8">
-        <v>46098.51854119213</v>
+        <v>46098.6852078588</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>213</v>
@@ -5000,13 +5000,13 @@
         <v>217</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.49949688658</v>
+        <v>46073.66616355324</v>
       </c>
       <c r="C60" s="5">
-        <v>46105.53175085648</v>
+        <v>46105.69841752315</v>
       </c>
       <c r="D60" s="5">
-        <v>46105.595200752316</v>
+        <v>46105.76186741898</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -5065,13 +5065,13 @@
         <v>220</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.499497233795</v>
+        <v>46073.66616390046</v>
       </c>
       <c r="C61" s="8">
-        <v>46128.602597476856</v>
+        <v>46128.76926414351</v>
       </c>
       <c r="D61" s="8">
-        <v>46128.602609062495</v>
+        <v>46128.769275729166</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>221</v>
@@ -5118,13 +5118,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4994975463</v>
+        <v>46073.66616421296</v>
       </c>
       <c r="C62" s="5">
-        <v>46105.595783425924</v>
+        <v>46105.76245009259</v>
       </c>
       <c r="D62" s="5">
-        <v>46105.59579931713</v>
+        <v>46105.7624659838</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5183,13 +5183,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.49949862268</v>
+        <v>46073.66616528935</v>
       </c>
       <c r="C63" s="8">
-        <v>46128.326897719904</v>
+        <v>46128.493564386576</v>
       </c>
       <c r="D63" s="8">
-        <v>46128.603114791666</v>
+        <v>46128.76978145834</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5248,13 +5248,13 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.49949893518</v>
+        <v>46073.666165601855</v>
       </c>
       <c r="C64" s="5">
-        <v>46128.60258145833</v>
+        <v>46128.769248125</v>
       </c>
       <c r="D64" s="5">
-        <v>46128.60259846065</v>
+        <v>46128.76926512731</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5313,13 +5313,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.49949923611</v>
+        <v>46073.666165902774</v>
       </c>
       <c r="C65" s="8">
-        <v>46120.50273689815</v>
+        <v>46120.66940356481</v>
       </c>
       <c r="D65" s="8">
-        <v>46129.3941137963</v>
+        <v>46129.56078046296</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>210</v>
@@ -5366,13 +5366,13 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.49949353009</v>
+        <v>46073.666160196764</v>
       </c>
       <c r="C66" s="5">
-        <v>46113.65978219907</v>
+        <v>46113.826448865744</v>
       </c>
       <c r="D66" s="5">
-        <v>46121.0390146412</v>
+        <v>46121.20568130787</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>
@@ -5431,13 +5431,13 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.499493310184</v>
+        <v>46073.666159976856</v>
       </c>
       <c r="C67" s="8">
-        <v>46113.65980471065</v>
+        <v>46113.82647137731</v>
       </c>
       <c r="D67" s="8">
-        <v>46113.659806400465</v>
+        <v>46113.82647306713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5496,13 +5496,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.49949299768</v>
+        <v>46073.66615966435</v>
       </c>
       <c r="C68" s="5">
-        <v>46120.50192715278</v>
+        <v>46120.66859381944</v>
       </c>
       <c r="D68" s="5">
-        <v>46120.50194306713</v>
+        <v>46120.668609733795</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>55</v>
@@ -5561,13 +5561,13 @@
         <v>244</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.49949958333</v>
+        <v>46073.66616625</v>
       </c>
       <c r="C69" s="8">
-        <v>46120.502533032406</v>
+        <v>46120.66919969907</v>
       </c>
       <c r="D69" s="8">
-        <v>46120.50254931713</v>
+        <v>46120.6692159838</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>245</v>
@@ -5626,13 +5626,13 @@
         <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46077.46202542824</v>
+        <v>46077.628692094906</v>
       </c>
       <c r="C70" s="5">
-        <v>46120.502574502316</v>
+        <v>46120.66924116898</v>
       </c>
       <c r="D70" s="5">
-        <v>46120.50258914352</v>
+        <v>46120.669255810186</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>248</v>
@@ -5691,13 +5691,13 @@
         <v>250</v>
       </c>
       <c r="B71" s="8">
-        <v>46099.376231111106</v>
+        <v>46099.54289777778</v>
       </c>
       <c r="C71" s="8">
-        <v>46126.68080083333</v>
+        <v>46126.8474675</v>
       </c>
       <c r="D71" s="8">
-        <v>46126.680802476854</v>
+        <v>46126.84746914352</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>251</v>
@@ -5754,13 +5754,13 @@
         <v>253</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.49949376157</v>
+        <v>46073.66616042824</v>
       </c>
       <c r="C72" s="5">
-        <v>46161.743501944446</v>
+        <v>46161.91016861111</v>
       </c>
       <c r="D72" s="5">
-        <v>46161.74351375</v>
+        <v>46161.91018041667</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>254</v>
@@ -5807,13 +5807,13 @@
         <v>256</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.49949402778</v>
+        <v>46073.66616069444</v>
       </c>
       <c r="C73" s="8">
-        <v>46133.46370634259</v>
+        <v>46133.63037300926</v>
       </c>
       <c r="D73" s="8">
-        <v>46133.474315520834</v>
+        <v>46133.6409821875</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>257</v>
@@ -5872,13 +5872,13 @@
         <v>259</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.49949425926</v>
+        <v>46073.666160925924</v>
       </c>
       <c r="C74" s="5">
-        <v>46133.46440752315</v>
+        <v>46133.63107418982</v>
       </c>
       <c r="D74" s="5">
-        <v>46133.464422199075</v>
+        <v>46133.63108886574</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>239</v>
@@ -5937,13 +5937,13 @@
         <v>262</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.49949450231</v>
+        <v>46073.66616116898</v>
       </c>
       <c r="C75" s="8">
-        <v>46133.46520177083</v>
+        <v>46133.6318684375</v>
       </c>
       <c r="D75" s="8">
-        <v>46133.6579886574</v>
+        <v>46133.824655324075</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>242</v>
@@ -6002,13 +6002,13 @@
         <v>265</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.49949475694</v>
+        <v>46073.66616142361</v>
       </c>
       <c r="C76" s="5">
-        <v>46148.27068769676</v>
+        <v>46148.43735436343</v>
       </c>
       <c r="D76" s="5">
-        <v>46148.27070649306</v>
+        <v>46148.43737315972</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>246</v>
@@ -6067,13 +6067,13 @@
         <v>267</v>
       </c>
       <c r="B77" s="8">
-        <v>46077.6559583912</v>
+        <v>46077.822625057874</v>
       </c>
       <c r="C77" s="8">
-        <v>46133.465182430555</v>
+        <v>46133.63184909722</v>
       </c>
       <c r="D77" s="8">
-        <v>46133.4652003125</v>
+        <v>46133.631866979165</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>249</v>
@@ -6132,13 +6132,13 @@
         <v>269</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.499494965276</v>
+        <v>46073.66616163195</v>
       </c>
       <c r="C78" s="5">
-        <v>46157.31385315972</v>
+        <v>46157.48051982639</v>
       </c>
       <c r="D78" s="5">
-        <v>46157.393249305554</v>
+        <v>46157.55991597222</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>207</v>
@@ -6197,13 +6197,13 @@
         <v>272</v>
       </c>
       <c r="B79" s="8">
-        <v>46073.49949519676</v>
+        <v>46073.666161863424</v>
       </c>
       <c r="C79" s="8">
-        <v>46161.74348398148</v>
+        <v>46161.91015064815</v>
       </c>
       <c r="D79" s="8">
-        <v>46174.49045946759</v>
+        <v>46174.65712613426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>273</v>
@@ -6262,13 +6262,13 @@
         <v>275</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.49949351852</v>
+        <v>46073.66616018518</v>
       </c>
       <c r="C80" s="5">
-        <v>46174.49026890047</v>
+        <v>46174.65693556713</v>
       </c>
       <c r="D80" s="5">
-        <v>46174.49037211806</v>
+        <v>46174.65703878472</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>276</v>
@@ -6315,13 +6315,13 @@
         <v>278</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.499493877316</v>
+        <v>46073.66616054398</v>
       </c>
       <c r="C81" s="8">
-        <v>46161.74285855324</v>
+        <v>46161.909525219904</v>
       </c>
       <c r="D81" s="8">
-        <v>46174.49044193287</v>
+        <v>46174.65710859954</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>279</v>
@@ -6380,13 +6380,13 @@
         <v>281</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.499494143514</v>
+        <v>46073.666160810186</v>
       </c>
       <c r="C82" s="5">
-        <v>46161.74280395833</v>
+        <v>46161.909470625</v>
       </c>
       <c r="D82" s="5">
-        <v>46174.49044245371</v>
+        <v>46174.657109120366</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>252</v>
@@ -6445,13 +6445,13 @@
         <v>284</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.499494421296</v>
+        <v>46073.66616108797</v>
       </c>
       <c r="C83" s="8">
-        <v>46142.7623125463</v>
+        <v>46142.928979212964</v>
       </c>
       <c r="D83" s="8">
-        <v>46174.490442951384</v>
+        <v>46174.657109618056</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>285</v>
@@ -6510,13 +6510,13 @@
         <v>287</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.499494675925</v>
+        <v>46073.6661613426</v>
       </c>
       <c r="C84" s="5">
-        <v>46174.490250069444</v>
+        <v>46174.656916736116</v>
       </c>
       <c r="D84" s="5">
-        <v>46174.49026893519</v>
+        <v>46174.65693560185</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>288</v>
@@ -6575,11 +6575,11 @@
         <v>290</v>
       </c>
       <c r="B85" s="8">
-        <v>46073.49949494213</v>
+        <v>46073.666161608795</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46091.53342930556</v>
+        <v>46091.70009597222</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>291</v>
@@ -6628,11 +6628,11 @@
         <v>293</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.49949523148</v>
+        <v>46073.666161898145</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46174.49027199074</v>
+        <v>46174.65693865741</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>294</v>
@@ -6691,11 +6691,11 @@
         <v>298</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.49949556713</v>
+        <v>46073.6661622338</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46174.49027203704</v>
+        <v>46174.6569387037</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>299</v>
@@ -6754,11 +6754,11 @@
         <v>301</v>
       </c>
       <c r="B88" s="5">
-        <v>46091.50207081018</v>
+        <v>46091.66873747685</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46091.53438923611</v>
+        <v>46091.70105590278</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>302</v>
@@ -6807,11 +6807,11 @@
         <v>304</v>
       </c>
       <c r="B89" s="8">
-        <v>46091.50212572917</v>
+        <v>46091.66879239584</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46174.49027255787</v>
+        <v>46174.65693922454</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>305</v>
@@ -6870,11 +6870,11 @@
         <v>307</v>
       </c>
       <c r="B90" s="5">
-        <v>46091.5023269213</v>
+        <v>46091.66899358796</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46157.03135275463</v>
+        <v>46157.198019421296</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>308</v>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.66615903935</v>
+        <v>46073.499492372684</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72419498843</v>
+        <v>46092.55752832176</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.530560405095</v>
+        <v>46097.363893738424</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1613,13 +1613,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.66615939815</v>
+        <v>46073.499492731484</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72416780093</v>
+        <v>46092.55750113426</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.87806965278</v>
+        <v>46133.71140298611</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1678,13 +1678,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.66615962963</v>
+        <v>46073.49949296296</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.724168298606</v>
+        <v>46092.55750163195</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.7241959838</v>
+        <v>46092.55752931713</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1743,13 +1743,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.66615988426</v>
+        <v>46073.49949321759</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.724168726854</v>
+        <v>46092.55750206018</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72419625</v>
+        <v>46092.55752958333</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1808,13 +1808,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.666160231485</v>
+        <v>46073.499493564814</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72416920139</v>
+        <v>46092.55750253472</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.76511025463</v>
+        <v>46100.598443587965</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1873,13 +1873,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.66616047454</v>
+        <v>46073.499493807874</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72416982639</v>
+        <v>46092.557503159725</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.7241962963</v>
+        <v>46092.55752962963</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1938,13 +1938,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.666160787034</v>
+        <v>46073.49949412037</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.60355960648</v>
+        <v>46129.43689293982</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.60357364583</v>
+        <v>46129.43690697917</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1991,13 +1991,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.66616105324</v>
+        <v>46073.499494386575</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.53196606482</v>
+        <v>46097.36529939815</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.53198291667</v>
+        <v>46097.36531625</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2056,13 +2056,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.66616129629</v>
+        <v>46073.49949462963</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.603544247686</v>
+        <v>46129.436877581014</v>
       </c>
       <c r="D12" s="5">
-        <v>46129.603824375</v>
+        <v>46129.43715770834</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2121,13 +2121,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.666161597226</v>
+        <v>46073.499494930555</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.53042917824</v>
+        <v>46097.36376251157</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.774145937496</v>
+        <v>46129.60747927084</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2170,13 +2170,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.66616013889</v>
+        <v>46073.49949347222</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.52783832176</v>
+        <v>46097.361171655095</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.527857037036</v>
+        <v>46097.36119037037</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2235,13 +2235,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.66616097222</v>
+        <v>46073.49949430556</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.53031609954</v>
+        <v>46097.36364943287</v>
       </c>
       <c r="D15" s="8">
-        <v>46100.76503991898</v>
+        <v>46100.59837325232</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2300,13 +2300,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.66616127315</v>
+        <v>46073.49949460648</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.52820017361</v>
+        <v>46097.36153350695</v>
       </c>
       <c r="D16" s="5">
-        <v>46100.765728252314</v>
+        <v>46100.59906158565</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2365,13 +2365,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.666161574074</v>
+        <v>46073.4994949074</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.53041068287</v>
+        <v>46097.3637440162</v>
       </c>
       <c r="D17" s="8">
-        <v>46133.6306210301</v>
+        <v>46133.463954363426</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2430,13 +2430,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.666161875</v>
+        <v>46073.499495208336</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.79754208333</v>
+        <v>46107.63087541667</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.63072813657</v>
+        <v>46133.46406146991</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2479,13 +2479,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.666162442125</v>
+        <v>46073.49949577547</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.5306434838</v>
+        <v>46097.36397681713</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.53065947916</v>
+        <v>46097.363992812505</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2544,13 +2544,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.66616216435</v>
+        <v>46073.49949549769</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.53069637732</v>
+        <v>46097.36402971065</v>
       </c>
       <c r="D20" s="5">
-        <v>46133.6306669676</v>
+        <v>46133.464000300926</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2609,13 +2609,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.66616271991</v>
+        <v>46073.49949605324</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.53204369213</v>
+        <v>46097.36537702546</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.53206203703</v>
+        <v>46097.36539537037</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2674,13 +2674,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.66616300926</v>
+        <v>46073.49949634259</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.53080361111</v>
+        <v>46097.364136944445</v>
       </c>
       <c r="D22" s="5">
-        <v>46100.764148229166</v>
+        <v>46100.5974815625</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2739,13 +2739,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.66616008102</v>
+        <v>46073.49949341435</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.53074555556</v>
+        <v>46097.36407888889</v>
       </c>
       <c r="D23" s="8">
-        <v>46100.76426966435</v>
+        <v>46100.59760299769</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2804,13 +2804,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46076.66316038194</v>
+        <v>46076.496493715276</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.797523402776</v>
+        <v>46107.63085673611</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.797543692126</v>
+        <v>46107.63087702546</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2869,13 +2869,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46099.53305806713</v>
+        <v>46099.366391400465</v>
       </c>
       <c r="C25" s="8">
-        <v>46099.53407392361</v>
+        <v>46099.36740725694</v>
       </c>
       <c r="D25" s="8">
-        <v>46133.6306462963</v>
+        <v>46133.463979629625</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2934,13 +2934,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.66616042824</v>
+        <v>46073.49949376157</v>
       </c>
       <c r="C26" s="5">
-        <v>46120.70601671297</v>
+        <v>46120.539350046296</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.63083221065</v>
+        <v>46133.46416554398</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2983,13 +2983,13 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.66616130787</v>
+        <v>46073.499494641204</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.80060909722</v>
+        <v>46107.633942430555</v>
       </c>
       <c r="D27" s="8">
-        <v>46133.63077927083</v>
+        <v>46133.46411260417</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -3048,13 +3048,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.66616162037</v>
+        <v>46073.49949495371</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.53139914352</v>
+        <v>46097.36473247685</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.53140097222</v>
+        <v>46097.364734305556</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3109,13 +3109,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.66616197917</v>
+        <v>46073.4994953125</v>
       </c>
       <c r="C29" s="8">
-        <v>46107.80055341435</v>
+        <v>46107.63388674769</v>
       </c>
       <c r="D29" s="8">
-        <v>46107.80055459491</v>
+        <v>46107.63388792824</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3170,13 +3170,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.66616234954</v>
+        <v>46073.499495682874</v>
       </c>
       <c r="C30" s="5">
-        <v>46107.80059315972</v>
+        <v>46107.63392649306</v>
       </c>
       <c r="D30" s="5">
-        <v>46107.80059462963</v>
+        <v>46107.63392796296</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3231,13 +3231,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.66616068287</v>
+        <v>46073.4994940162</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.53132358796</v>
+        <v>46097.3646569213</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.531336203705</v>
+        <v>46097.36466953704</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3296,13 +3296,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.6661609838</v>
+        <v>46073.49949431713</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.53127260417</v>
+        <v>46097.3646059375</v>
       </c>
       <c r="D32" s="5">
-        <v>46099.5338058912</v>
+        <v>46099.36713922454</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3357,13 +3357,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.66616126157</v>
+        <v>46073.49949459491</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.53131013889</v>
+        <v>46097.36464347222</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.53131167824</v>
+        <v>46097.36464501158</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3418,13 +3418,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.6661615162</v>
+        <v>46073.49949484954</v>
       </c>
       <c r="C34" s="5">
-        <v>46120.668502002314</v>
+        <v>46120.50183533565</v>
       </c>
       <c r="D34" s="5">
-        <v>46120.66851498843</v>
+        <v>46120.50184832176</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3483,13 +3483,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.66616178241</v>
+        <v>46073.49949511574</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.53208601852</v>
+        <v>46097.36541935185</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.53208754629</v>
+        <v>46097.36542087963</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3544,13 +3544,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.66616206018</v>
+        <v>46073.499495393524</v>
       </c>
       <c r="C36" s="5">
-        <v>46120.668486828705</v>
+        <v>46120.50182016204</v>
       </c>
       <c r="D36" s="5">
-        <v>46120.66848849537</v>
+        <v>46120.5018218287</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3605,13 +3605,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.66616232639</v>
+        <v>46073.49949565972</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.79872496528</v>
+        <v>46107.63205829861</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.79873737269</v>
+        <v>46107.63207070602</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3670,13 +3670,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.66616260417</v>
+        <v>46073.4994959375</v>
       </c>
       <c r="C38" s="5">
-        <v>46107.79861873842</v>
+        <v>46107.63195207176</v>
       </c>
       <c r="D38" s="5">
-        <v>46107.798620173606</v>
+        <v>46107.63195350695</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3731,13 +3731,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.66616087963</v>
+        <v>46073.49949421296</v>
       </c>
       <c r="C39" s="8">
-        <v>46107.798710462965</v>
+        <v>46107.6320437963</v>
       </c>
       <c r="D39" s="8">
-        <v>46107.79871178241</v>
+        <v>46107.63204511574</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3792,13 +3792,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.666162685186</v>
+        <v>46073.499496018514</v>
       </c>
       <c r="C40" s="5">
-        <v>46098.681831608796</v>
+        <v>46098.51516494213</v>
       </c>
       <c r="D40" s="5">
-        <v>46098.682025243055</v>
+        <v>46098.51535857639</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3857,13 +3857,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.66616299769</v>
+        <v>46073.49949633102</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.531549004634</v>
+        <v>46097.36488233796</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.531550381944</v>
+        <v>46097.36488371528</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3918,13 +3918,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.66616332176</v>
+        <v>46073.49949665509</v>
       </c>
       <c r="C42" s="5">
-        <v>46098.68181620371</v>
+        <v>46098.51514953704</v>
       </c>
       <c r="D42" s="5">
-        <v>46098.68181796296</v>
+        <v>46098.51515129629</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3979,13 +3979,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.680800381946</v>
+        <v>46076.514133715275</v>
       </c>
       <c r="C43" s="8">
-        <v>46107.80085251157</v>
+        <v>46107.63418584491</v>
       </c>
       <c r="D43" s="8">
-        <v>46107.80089184028</v>
+        <v>46107.634225173606</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4044,13 +4044,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.68351988426</v>
+        <v>46076.51685321759</v>
       </c>
       <c r="C44" s="5">
-        <v>46107.79885972222</v>
+        <v>46107.63219305556</v>
       </c>
       <c r="D44" s="5">
-        <v>46107.79886152778</v>
+        <v>46107.632194861115</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4109,13 +4109,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46076.68374787037</v>
+        <v>46076.5170812037</v>
       </c>
       <c r="C45" s="8">
-        <v>46107.80083613426</v>
+        <v>46107.634169467594</v>
       </c>
       <c r="D45" s="8">
-        <v>46107.80083771991</v>
+        <v>46107.63417105324</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4174,13 +4174,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46099.5301296875</v>
+        <v>46099.36346302083</v>
       </c>
       <c r="C46" s="5">
-        <v>46120.66386724537</v>
+        <v>46120.4972005787</v>
       </c>
       <c r="D46" s="5">
-        <v>46133.63092840278</v>
+        <v>46133.46426173611</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4239,13 +4239,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="8">
-        <v>46099.53044444445</v>
+        <v>46099.36377777778</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.80117576389</v>
+        <v>46107.63450909722</v>
       </c>
       <c r="D47" s="8">
-        <v>46107.80117737269</v>
+        <v>46107.63451070602</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>101</v>
@@ -4294,13 +4294,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46099.53058535879</v>
+        <v>46099.36391869213</v>
       </c>
       <c r="C48" s="5">
-        <v>46120.664315358794</v>
+        <v>46120.49764869213</v>
       </c>
       <c r="D48" s="5">
-        <v>46120.664316898146</v>
+        <v>46120.49765023148</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>169</v>
@@ -4349,13 +4349,13 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46099.84979115741</v>
+        <v>46099.68312449074</v>
       </c>
       <c r="C49" s="8">
-        <v>46105.754452037036</v>
+        <v>46105.58778537037</v>
       </c>
       <c r="D49" s="8">
-        <v>46120.64216769676</v>
+        <v>46120.475501030094</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4404,13 +4404,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46099.84984650463</v>
+        <v>46099.683179837964</v>
       </c>
       <c r="C50" s="5">
-        <v>46120.66462393518</v>
+        <v>46120.49795726852</v>
       </c>
       <c r="D50" s="5">
-        <v>46120.664625185185</v>
+        <v>46120.49795851852</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4459,13 +4459,13 @@
         <v>181</v>
       </c>
       <c r="B51" s="8">
-        <v>46099.85031037037</v>
+        <v>46099.683643703705</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.66463579861</v>
+        <v>46120.497969131946</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.66463688658</v>
+        <v>46120.497970219905</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -4514,13 +4514,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46099.53128005787</v>
+        <v>46099.364613391204</v>
       </c>
       <c r="C52" s="5">
-        <v>46120.64085998843</v>
+        <v>46120.47419332176</v>
       </c>
       <c r="D52" s="5">
-        <v>46120.66432236111</v>
+        <v>46120.497655694446</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>185</v>
@@ -4569,13 +4569,13 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.66616363426</v>
+        <v>46073.49949696759</v>
       </c>
       <c r="C53" s="8">
-        <v>46171.70100961806</v>
+        <v>46171.53434295139</v>
       </c>
       <c r="D53" s="8">
-        <v>46171.70102094907</v>
+        <v>46171.53435428241</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>189</v>
@@ -4622,13 +4622,13 @@
         <v>191</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.66616400463</v>
+        <v>46073.499497337965</v>
       </c>
       <c r="C54" s="5">
-        <v>46098.52111122685</v>
+        <v>46098.35444456019</v>
       </c>
       <c r="D54" s="5">
-        <v>46098.521133449074</v>
+        <v>46098.3544667824</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -4687,13 +4687,13 @@
         <v>196</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.666162152775</v>
+        <v>46073.49949548611</v>
       </c>
       <c r="C55" s="8">
-        <v>46114.787797592595</v>
+        <v>46114.62113092592</v>
       </c>
       <c r="D55" s="8">
-        <v>46114.78779920139</v>
+        <v>46114.621132534725</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>197</v>
@@ -4752,13 +4752,13 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46091.66724454861</v>
+        <v>46091.50057788195</v>
       </c>
       <c r="C56" s="5">
-        <v>46114.78789839121</v>
+        <v>46114.62123172454</v>
       </c>
       <c r="D56" s="5">
-        <v>46114.787913576394</v>
+        <v>46114.62124690972</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4817,13 +4817,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46091.66727622686</v>
+        <v>46091.500609560186</v>
       </c>
       <c r="C57" s="8">
-        <v>46171.70098944445</v>
+        <v>46171.53432277778</v>
       </c>
       <c r="D57" s="8">
-        <v>46171.70101023148</v>
+        <v>46171.53434356481</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>204</v>
@@ -4882,13 +4882,13 @@
         <v>209</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.666162615744</v>
+        <v>46073.49949594907</v>
       </c>
       <c r="C58" s="5">
-        <v>46105.6984371875</v>
+        <v>46105.53177052083</v>
       </c>
       <c r="D58" s="5">
-        <v>46105.69845173611</v>
+        <v>46105.53178506944</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>210</v>
@@ -4935,13 +4935,13 @@
         <v>212</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.666163182876</v>
+        <v>46073.499496516204</v>
       </c>
       <c r="C59" s="8">
-        <v>46098.68519152778</v>
+        <v>46098.51852486111</v>
       </c>
       <c r="D59" s="8">
-        <v>46098.6852078588</v>
+        <v>46098.51854119213</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>213</v>
@@ -5000,13 +5000,13 @@
         <v>217</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.66616355324</v>
+        <v>46073.49949688658</v>
       </c>
       <c r="C60" s="5">
-        <v>46105.69841752315</v>
+        <v>46105.53175085648</v>
       </c>
       <c r="D60" s="5">
-        <v>46105.76186741898</v>
+        <v>46105.595200752316</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -5065,13 +5065,13 @@
         <v>220</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.66616390046</v>
+        <v>46073.499497233795</v>
       </c>
       <c r="C61" s="8">
-        <v>46128.76926414351</v>
+        <v>46128.602597476856</v>
       </c>
       <c r="D61" s="8">
-        <v>46128.769275729166</v>
+        <v>46128.602609062495</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>221</v>
@@ -5118,13 +5118,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.66616421296</v>
+        <v>46073.4994975463</v>
       </c>
       <c r="C62" s="5">
-        <v>46105.76245009259</v>
+        <v>46105.595783425924</v>
       </c>
       <c r="D62" s="5">
-        <v>46105.7624659838</v>
+        <v>46105.59579931713</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5183,13 +5183,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.66616528935</v>
+        <v>46073.49949862268</v>
       </c>
       <c r="C63" s="8">
-        <v>46128.493564386576</v>
+        <v>46128.326897719904</v>
       </c>
       <c r="D63" s="8">
-        <v>46128.76978145834</v>
+        <v>46128.603114791666</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5248,13 +5248,13 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.666165601855</v>
+        <v>46073.49949893518</v>
       </c>
       <c r="C64" s="5">
-        <v>46128.769248125</v>
+        <v>46128.60258145833</v>
       </c>
       <c r="D64" s="5">
-        <v>46128.76926512731</v>
+        <v>46128.60259846065</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5313,13 +5313,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.666165902774</v>
+        <v>46073.49949923611</v>
       </c>
       <c r="C65" s="8">
-        <v>46120.66940356481</v>
+        <v>46120.50273689815</v>
       </c>
       <c r="D65" s="8">
-        <v>46129.56078046296</v>
+        <v>46129.3941137963</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>210</v>
@@ -5366,13 +5366,13 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.666160196764</v>
+        <v>46073.49949353009</v>
       </c>
       <c r="C66" s="5">
-        <v>46113.826448865744</v>
+        <v>46113.65978219907</v>
       </c>
       <c r="D66" s="5">
-        <v>46121.20568130787</v>
+        <v>46121.0390146412</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>
@@ -5431,13 +5431,13 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.666159976856</v>
+        <v>46073.499493310184</v>
       </c>
       <c r="C67" s="8">
-        <v>46113.82647137731</v>
+        <v>46113.65980471065</v>
       </c>
       <c r="D67" s="8">
-        <v>46113.82647306713</v>
+        <v>46113.659806400465</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5496,13 +5496,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.66615966435</v>
+        <v>46073.49949299768</v>
       </c>
       <c r="C68" s="5">
-        <v>46120.66859381944</v>
+        <v>46120.50192715278</v>
       </c>
       <c r="D68" s="5">
-        <v>46120.668609733795</v>
+        <v>46120.50194306713</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>55</v>
@@ -5561,13 +5561,13 @@
         <v>244</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.66616625</v>
+        <v>46073.49949958333</v>
       </c>
       <c r="C69" s="8">
-        <v>46120.66919969907</v>
+        <v>46120.502533032406</v>
       </c>
       <c r="D69" s="8">
-        <v>46120.6692159838</v>
+        <v>46120.50254931713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>245</v>
@@ -5626,13 +5626,13 @@
         <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46077.628692094906</v>
+        <v>46077.46202542824</v>
       </c>
       <c r="C70" s="5">
-        <v>46120.66924116898</v>
+        <v>46120.502574502316</v>
       </c>
       <c r="D70" s="5">
-        <v>46120.669255810186</v>
+        <v>46120.50258914352</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>248</v>
@@ -5691,13 +5691,13 @@
         <v>250</v>
       </c>
       <c r="B71" s="8">
-        <v>46099.54289777778</v>
+        <v>46099.376231111106</v>
       </c>
       <c r="C71" s="8">
-        <v>46126.8474675</v>
+        <v>46126.68080083333</v>
       </c>
       <c r="D71" s="8">
-        <v>46126.84746914352</v>
+        <v>46126.680802476854</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>251</v>
@@ -5754,13 +5754,13 @@
         <v>253</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.66616042824</v>
+        <v>46073.49949376157</v>
       </c>
       <c r="C72" s="5">
-        <v>46161.91016861111</v>
+        <v>46161.743501944446</v>
       </c>
       <c r="D72" s="5">
-        <v>46161.91018041667</v>
+        <v>46161.74351375</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>254</v>
@@ -5807,13 +5807,13 @@
         <v>256</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.66616069444</v>
+        <v>46073.49949402778</v>
       </c>
       <c r="C73" s="8">
-        <v>46133.63037300926</v>
+        <v>46133.46370634259</v>
       </c>
       <c r="D73" s="8">
-        <v>46133.6409821875</v>
+        <v>46133.474315520834</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>257</v>
@@ -5872,13 +5872,13 @@
         <v>259</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.666160925924</v>
+        <v>46073.49949425926</v>
       </c>
       <c r="C74" s="5">
-        <v>46133.63107418982</v>
+        <v>46133.46440752315</v>
       </c>
       <c r="D74" s="5">
-        <v>46133.63108886574</v>
+        <v>46133.464422199075</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>239</v>
@@ -5937,13 +5937,13 @@
         <v>262</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.66616116898</v>
+        <v>46073.49949450231</v>
       </c>
       <c r="C75" s="8">
-        <v>46133.6318684375</v>
+        <v>46133.46520177083</v>
       </c>
       <c r="D75" s="8">
-        <v>46133.824655324075</v>
+        <v>46133.6579886574</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>242</v>
@@ -6002,13 +6002,13 @@
         <v>265</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.66616142361</v>
+        <v>46073.49949475694</v>
       </c>
       <c r="C76" s="5">
-        <v>46148.43735436343</v>
+        <v>46148.27068769676</v>
       </c>
       <c r="D76" s="5">
-        <v>46148.43737315972</v>
+        <v>46148.27070649306</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>246</v>
@@ -6067,13 +6067,13 @@
         <v>267</v>
       </c>
       <c r="B77" s="8">
-        <v>46077.822625057874</v>
+        <v>46077.6559583912</v>
       </c>
       <c r="C77" s="8">
-        <v>46133.63184909722</v>
+        <v>46133.465182430555</v>
       </c>
       <c r="D77" s="8">
-        <v>46133.631866979165</v>
+        <v>46133.4652003125</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>249</v>
@@ -6132,13 +6132,13 @@
         <v>269</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.66616163195</v>
+        <v>46073.499494965276</v>
       </c>
       <c r="C78" s="5">
-        <v>46157.48051982639</v>
+        <v>46157.31385315972</v>
       </c>
       <c r="D78" s="5">
-        <v>46157.55991597222</v>
+        <v>46157.393249305554</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>207</v>
@@ -6197,13 +6197,13 @@
         <v>272</v>
       </c>
       <c r="B79" s="8">
-        <v>46073.666161863424</v>
+        <v>46073.49949519676</v>
       </c>
       <c r="C79" s="8">
-        <v>46161.91015064815</v>
+        <v>46161.74348398148</v>
       </c>
       <c r="D79" s="8">
-        <v>46174.65712613426</v>
+        <v>46174.49045946759</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>273</v>
@@ -6262,13 +6262,13 @@
         <v>275</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.66616018518</v>
+        <v>46073.49949351852</v>
       </c>
       <c r="C80" s="5">
-        <v>46174.65693556713</v>
+        <v>46174.49026890047</v>
       </c>
       <c r="D80" s="5">
-        <v>46174.65703878472</v>
+        <v>46174.49037211806</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>276</v>
@@ -6315,13 +6315,13 @@
         <v>278</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.66616054398</v>
+        <v>46073.499493877316</v>
       </c>
       <c r="C81" s="8">
-        <v>46161.909525219904</v>
+        <v>46161.74285855324</v>
       </c>
       <c r="D81" s="8">
-        <v>46174.65710859954</v>
+        <v>46174.49044193287</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>279</v>
@@ -6380,13 +6380,13 @@
         <v>281</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.666160810186</v>
+        <v>46073.499494143514</v>
       </c>
       <c r="C82" s="5">
-        <v>46161.909470625</v>
+        <v>46161.74280395833</v>
       </c>
       <c r="D82" s="5">
-        <v>46174.657109120366</v>
+        <v>46174.49044245371</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>252</v>
@@ -6445,13 +6445,13 @@
         <v>284</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.66616108797</v>
+        <v>46073.499494421296</v>
       </c>
       <c r="C83" s="8">
-        <v>46142.928979212964</v>
+        <v>46142.7623125463</v>
       </c>
       <c r="D83" s="8">
-        <v>46174.657109618056</v>
+        <v>46174.490442951384</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>285</v>
@@ -6510,13 +6510,13 @@
         <v>287</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.6661613426</v>
+        <v>46073.499494675925</v>
       </c>
       <c r="C84" s="5">
-        <v>46174.656916736116</v>
+        <v>46174.490250069444</v>
       </c>
       <c r="D84" s="5">
-        <v>46174.65693560185</v>
+        <v>46174.49026893519</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>288</v>
@@ -6575,11 +6575,11 @@
         <v>290</v>
       </c>
       <c r="B85" s="8">
-        <v>46073.666161608795</v>
+        <v>46073.49949494213</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46091.70009597222</v>
+        <v>46091.53342930556</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>291</v>
@@ -6628,11 +6628,11 @@
         <v>293</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.666161898145</v>
+        <v>46073.49949523148</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46174.65693865741</v>
+        <v>46174.49027199074</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>294</v>
@@ -6691,11 +6691,11 @@
         <v>298</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.6661622338</v>
+        <v>46073.49949556713</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46174.6569387037</v>
+        <v>46174.49027203704</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>299</v>
@@ -6754,11 +6754,11 @@
         <v>301</v>
       </c>
       <c r="B88" s="5">
-        <v>46091.66873747685</v>
+        <v>46091.50207081018</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46091.70105590278</v>
+        <v>46091.53438923611</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>302</v>
@@ -6807,11 +6807,11 @@
         <v>304</v>
       </c>
       <c r="B89" s="8">
-        <v>46091.66879239584</v>
+        <v>46091.50212572917</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46174.65693922454</v>
+        <v>46174.49027255787</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>305</v>
@@ -6870,11 +6870,11 @@
         <v>307</v>
       </c>
       <c r="B90" s="5">
-        <v>46091.66899358796</v>
+        <v>46091.5023269213</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46157.198019421296</v>
+        <v>46157.03135275463</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>308</v>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="306">
   <si>
     <t>50001477- TRITON MINERA</t>
   </si>
@@ -280,9 +280,6 @@
     <t>propuesta nucleo  rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
@@ -290,12 +287,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -2689,11 +2680,9 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>45978</v>
       </c>
@@ -2716,7 +2705,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="5">
         <v>45978</v>
@@ -2736,7 +2725,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46073.66616008102</v>
@@ -2748,17 +2737,15 @@
         <v>46100.76426966435</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>94</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8">
         <v>45978</v>
       </c>
@@ -2781,7 +2768,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="8">
         <v>45978</v>
@@ -2801,7 +2788,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46076.66316038194</v>
@@ -2813,7 +2800,7 @@
         <v>46107.797543692126</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2846,7 +2833,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="5">
         <v>45978</v>
@@ -2866,7 +2853,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46099.53305806713</v>
@@ -2878,7 +2865,7 @@
         <v>46133.6306462963</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2911,7 +2898,7 @@
         <v>69</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q25" s="8">
         <v>45978</v>
@@ -2931,7 +2918,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46073.66616042824</v>
@@ -2943,7 +2930,7 @@
         <v>46133.63083221065</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -2967,7 +2954,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -2980,7 +2967,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B27" s="8">
         <v>46073.66616130787</v>
@@ -2992,16 +2979,16 @@
         <v>46133.63077927083</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I27" s="8">
         <v>45973</v>
@@ -3019,13 +3006,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="8">
         <v>45973</v>
@@ -3045,7 +3032,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5">
         <v>46073.66616162037</v>
@@ -3057,16 +3044,16 @@
         <v>46097.53140097222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I28" s="5">
         <v>45973</v>
@@ -3084,29 +3071,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46073.66616197917</v>
@@ -3118,16 +3105,16 @@
         <v>46107.80055459491</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I29" s="8">
         <v>45993</v>
@@ -3145,29 +3132,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46073.66616234954</v>
@@ -3179,16 +3166,16 @@
         <v>46107.80059462963</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I30" s="5">
         <v>45993</v>
@@ -3206,29 +3193,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46073.66616068287</v>
@@ -3240,16 +3227,16 @@
         <v>46097.531336203705</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I31" s="8">
         <v>45980</v>
@@ -3267,13 +3254,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q31" s="8">
         <v>45980</v>
@@ -3293,7 +3280,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46073.6661609838</v>
@@ -3305,16 +3292,16 @@
         <v>46099.5338058912</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I32" s="5">
         <v>45980</v>
@@ -3332,29 +3319,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46073.66616126157</v>
@@ -3366,16 +3353,16 @@
         <v>46097.53131167824</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I33" s="8">
         <v>45982</v>
@@ -3393,29 +3380,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="O33" s="9" t="s">
-        <v>125</v>
-      </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46073.6661615162</v>
@@ -3427,16 +3414,16 @@
         <v>46120.66851498843</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I34" s="5">
         <v>45975</v>
@@ -3454,13 +3441,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q34" s="5">
         <v>45975</v>
@@ -3480,7 +3467,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46073.66616178241</v>
@@ -3492,16 +3479,16 @@
         <v>46097.53208754629</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I35" s="8">
         <v>45975</v>
@@ -3519,29 +3506,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46073.66616206018</v>
@@ -3553,16 +3540,16 @@
         <v>46120.66848849537</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I36" s="5">
         <v>45986</v>
@@ -3580,29 +3567,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="O36" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="O36" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46073.66616232639</v>
@@ -3614,16 +3601,16 @@
         <v>46107.79873737269</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I37" s="8">
         <v>45980</v>
@@ -3641,13 +3628,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q37" s="8">
         <v>45980</v>
@@ -3667,7 +3654,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46073.66616260417</v>
@@ -3679,16 +3666,16 @@
         <v>46107.798620173606</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I38" s="5">
         <v>45980</v>
@@ -3706,29 +3693,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46073.66616087963</v>
@@ -3740,16 +3727,16 @@
         <v>46107.79871178241</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I39" s="8">
         <v>45982</v>
@@ -3767,29 +3754,29 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="O39" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="O39" s="9" t="s">
-        <v>143</v>
-      </c>
       <c r="P39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46073.666162685186</v>
@@ -3801,16 +3788,16 @@
         <v>46098.682025243055</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>45980</v>
@@ -3828,13 +3815,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q40" s="5">
         <v>45980</v>
@@ -3854,7 +3841,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46073.66616299769</v>
@@ -3866,16 +3853,16 @@
         <v>46097.531550381944</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I41" s="8">
         <v>45980</v>
@@ -3893,29 +3880,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46073.66616332176</v>
@@ -3927,16 +3914,16 @@
         <v>46098.68181796296</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I42" s="5">
         <v>46000</v>
@@ -3954,29 +3941,29 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46076.680800381946</v>
@@ -3988,16 +3975,16 @@
         <v>46107.80089184028</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I43" s="8">
         <v>45980</v>
@@ -4015,13 +4002,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="8">
         <v>45980</v>
@@ -4041,7 +4028,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46076.68351988426</v>
@@ -4053,16 +4040,16 @@
         <v>46107.79886152778</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I44" s="5">
         <v>45980</v>
@@ -4080,13 +4067,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="5">
         <v>45987</v>
@@ -4095,18 +4082,18 @@
         <v>46020</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46076.68374787037</v>
@@ -4118,16 +4105,16 @@
         <v>46107.80083771991</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I45" s="8">
         <v>46009</v>
@@ -4145,13 +4132,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="O45" s="9" t="s">
-        <v>163</v>
-      </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="8">
         <v>46021</v>
@@ -4160,18 +4147,18 @@
         <v>46101</v>
       </c>
       <c r="S45" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T45" s="9">
         <v>0</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46099.5301296875</v>
@@ -4183,16 +4170,16 @@
         <v>46133.63092840278</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I46" s="5">
         <v>45980</v>
@@ -4210,10 +4197,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4236,7 +4223,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46099.53044444445</v>
@@ -4248,16 +4235,16 @@
         <v>46107.80117737269</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I47" s="8">
         <v>45980</v>
@@ -4275,13 +4262,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4291,7 +4278,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46099.53058535879</v>
@@ -4303,16 +4290,16 @@
         <v>46120.664316898146</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I48" s="5">
         <v>45982</v>
@@ -4330,13 +4317,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4346,7 +4333,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46099.84979115741</v>
@@ -4358,16 +4345,16 @@
         <v>46120.64216769676</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I49" s="8">
         <v>45980</v>
@@ -4385,7 +4372,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>26</v>
@@ -4401,7 +4388,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46099.84984650463</v>
@@ -4413,16 +4400,16 @@
         <v>46120.664625185185</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I50" s="5">
         <v>45980</v>
@@ -4440,7 +4427,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>26</v>
@@ -4456,7 +4443,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46099.85031037037</v>
@@ -4468,16 +4455,16 @@
         <v>46120.66463688658</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I51" s="8">
         <v>45980</v>
@@ -4495,13 +4482,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4511,7 +4498,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46099.53128005787</v>
@@ -4523,16 +4510,16 @@
         <v>46120.66432236111</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46098</v>
@@ -4550,13 +4537,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4566,7 +4553,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46073.66616363426</v>
@@ -4578,7 +4565,7 @@
         <v>46171.70102094907</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4602,7 +4589,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4619,7 +4606,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46073.66616400463</v>
@@ -4631,16 +4618,16 @@
         <v>46098.521133449074</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>45978</v>
@@ -4658,13 +4645,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="5">
         <v>45978</v>
@@ -4684,7 +4671,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46073.666162152775</v>
@@ -4696,16 +4683,16 @@
         <v>46114.78779920139</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I55" s="8">
         <v>46031</v>
@@ -4723,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="8">
         <v>46031</v>
@@ -4749,7 +4736,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46091.66724454861</v>
@@ -4761,16 +4748,16 @@
         <v>46114.787913576394</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I56" s="5">
         <v>46038</v>
@@ -4788,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q56" s="5">
         <v>46038</v>
@@ -4814,7 +4801,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46091.66727622686</v>
@@ -4826,16 +4813,16 @@
         <v>46171.70101023148</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I57" s="8">
         <v>46126</v>
@@ -4853,13 +4840,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="8">
         <v>46126</v>
@@ -4879,7 +4866,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46073.666162615744</v>
@@ -4891,7 +4878,7 @@
         <v>46105.69845173611</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4915,7 +4902,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4932,7 +4919,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46073.666163182876</v>
@@ -4944,16 +4931,16 @@
         <v>46098.6852078588</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I59" s="8">
         <v>46029</v>
@@ -4971,13 +4958,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="8">
         <v>46029</v>
@@ -4997,7 +4984,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46073.66616355324</v>
@@ -5009,16 +4996,16 @@
         <v>46105.76186741898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I60" s="5">
         <v>46031</v>
@@ -5036,13 +5023,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="O60" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="O60" s="6" t="s">
-        <v>213</v>
-      </c>
       <c r="P60" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="5">
         <v>46031</v>
@@ -5062,7 +5049,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B61" s="8">
         <v>46073.66616390046</v>
@@ -5074,7 +5061,7 @@
         <v>46128.769275729166</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5098,7 +5085,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5115,7 +5102,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46073.66616421296</v>
@@ -5127,16 +5114,16 @@
         <v>46105.7624659838</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I62" s="5">
         <v>46035</v>
@@ -5154,13 +5141,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q62" s="5">
         <v>46035</v>
@@ -5180,7 +5167,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B63" s="8">
         <v>46073.66616528935</v>
@@ -5192,16 +5179,16 @@
         <v>46128.76978145834</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I63" s="8">
         <v>46044</v>
@@ -5219,13 +5206,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q63" s="8">
         <v>46044</v>
@@ -5245,7 +5232,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46073.666165601855</v>
@@ -5257,16 +5244,16 @@
         <v>46128.76926512731</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I64" s="5">
         <v>46073</v>
@@ -5284,13 +5271,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46073</v>
@@ -5310,7 +5297,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
         <v>46073.666165902774</v>
@@ -5322,7 +5309,7 @@
         <v>46129.56078046296</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5363,7 +5350,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46073.666160196764</v>
@@ -5375,16 +5362,16 @@
         <v>46121.20568130787</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I66" s="5">
         <v>46119</v>
@@ -5402,13 +5389,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="5">
         <v>46119</v>
@@ -5428,7 +5415,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B67" s="8">
         <v>46073.666159976856</v>
@@ -5440,16 +5427,16 @@
         <v>46113.82647306713</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I67" s="8">
         <v>46097</v>
@@ -5467,13 +5454,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="8">
         <v>46097</v>
@@ -5493,7 +5480,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
         <v>46073.66615966435</v>
@@ -5511,10 +5498,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I68" s="5">
         <v>46091</v>
@@ -5532,10 +5519,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>54</v>
@@ -5558,7 +5545,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B69" s="8">
         <v>46073.66616625</v>
@@ -5570,16 +5557,16 @@
         <v>46120.6692159838</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I69" s="8">
         <v>46031</v>
@@ -5597,13 +5584,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q69" s="8">
         <v>46031</v>
@@ -5623,7 +5610,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B70" s="5">
         <v>46077.628692094906</v>
@@ -5635,16 +5622,16 @@
         <v>46120.669255810186</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I70" s="5">
         <v>46087</v>
@@ -5662,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q70" s="5">
         <v>46087</v>
@@ -5688,7 +5675,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B71" s="8">
         <v>46099.54289777778</v>
@@ -5700,16 +5687,16 @@
         <v>46126.84746914352</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5725,13 +5712,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q71" s="8">
         <v>46100</v>
@@ -5751,7 +5738,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
         <v>46073.66616042824</v>
@@ -5763,7 +5750,7 @@
         <v>46161.91018041667</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5787,7 +5774,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5804,7 +5791,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B73" s="8">
         <v>46073.66616069444</v>
@@ -5816,17 +5803,15 @@
         <v>46133.6409821875</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
       <c r="I73" s="8">
         <v>46077</v>
       </c>
@@ -5843,13 +5828,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q73" s="8">
         <v>46077</v>
@@ -5869,7 +5854,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B74" s="5">
         <v>46073.666160925924</v>
@@ -5881,17 +5866,15 @@
         <v>46133.63108886574</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H74" s="6"/>
       <c r="I74" s="5">
         <v>46121</v>
       </c>
@@ -5908,13 +5891,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46121</v>
@@ -5934,7 +5917,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B75" s="8">
         <v>46073.66616116898</v>
@@ -5946,17 +5929,15 @@
         <v>46133.824655324075</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H75" s="9"/>
       <c r="I75" s="8">
         <v>46099</v>
       </c>
@@ -5973,13 +5954,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q75" s="8">
         <v>46099</v>
@@ -5999,7 +5980,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46073.66616142361</v>
@@ -6011,17 +5992,15 @@
         <v>46148.43737315972</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H76" s="6"/>
       <c r="I76" s="5">
         <v>46101</v>
       </c>
@@ -6038,13 +6017,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q76" s="5">
         <v>46101</v>
@@ -6064,7 +6043,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B77" s="8">
         <v>46077.822625057874</v>
@@ -6076,17 +6055,15 @@
         <v>46133.631866979165</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H77" s="9"/>
       <c r="I77" s="8">
         <v>46097</v>
       </c>
@@ -6103,13 +6080,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q77" s="8">
         <v>46097</v>
@@ -6129,7 +6106,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B78" s="5">
         <v>46073.66616163195</v>
@@ -6141,17 +6118,15 @@
         <v>46157.55991597222</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H78" s="6"/>
       <c r="I78" s="5">
         <v>46125</v>
       </c>
@@ -6168,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q78" s="5">
         <v>46125</v>
@@ -6194,7 +6169,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B79" s="8">
         <v>46073.666161863424</v>
@@ -6206,17 +6181,15 @@
         <v>46174.65712613426</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="9"/>
       <c r="I79" s="8">
         <v>46127</v>
       </c>
@@ -6233,13 +6206,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q79" s="8">
         <v>46127</v>
@@ -6259,7 +6232,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B80" s="5">
         <v>46073.66616018518</v>
@@ -6271,7 +6244,7 @@
         <v>46174.65703878472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6295,7 +6268,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6312,7 +6285,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B81" s="8">
         <v>46073.66616054398</v>
@@ -6324,7 +6297,7 @@
         <v>46174.65710859954</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6351,13 +6324,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="8">
         <v>46128</v>
@@ -6377,7 +6350,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46073.666160810186</v>
@@ -6389,17 +6362,15 @@
         <v>46174.657109120366</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="5">
         <v>46129</v>
       </c>
@@ -6416,13 +6387,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Q82" s="5">
         <v>46129</v>
@@ -6442,7 +6413,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46073.66616108797</v>
@@ -6454,16 +6425,16 @@
         <v>46174.657109618056</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I83" s="8">
         <v>46134</v>
@@ -6481,13 +6452,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="8">
         <v>46134</v>
@@ -6507,7 +6478,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46073.6661613426</v>
@@ -6519,16 +6490,16 @@
         <v>46174.65693560185</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I84" s="5">
         <v>46135</v>
@@ -6546,13 +6517,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="Q84" s="5">
         <v>46135</v>
@@ -6572,7 +6543,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B85" s="8">
         <v>46073.666161608795</v>
@@ -6582,7 +6553,7 @@
         <v>46091.70009597222</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6606,7 +6577,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6614,18 +6585,18 @@
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
       <c r="S85" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T85" s="9">
         <v>0</v>
       </c>
       <c r="U85" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B86" s="5">
         <v>46073.666161898145</v>
@@ -6635,16 +6606,16 @@
         <v>46174.65693865741</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I86" s="5">
         <v>46136</v>
@@ -6662,13 +6633,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>288</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>291</v>
       </c>
       <c r="Q86" s="5">
         <v>46136</v>
@@ -6683,12 +6654,12 @@
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B87" s="8">
         <v>46073.6661622338</v>
@@ -6698,16 +6669,16 @@
         <v>46174.6569387037</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I87" s="8">
         <v>46136</v>
@@ -6725,13 +6696,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q87" s="8">
         <v>46136</v>
@@ -6746,12 +6717,12 @@
         <v>0</v>
       </c>
       <c r="U87" s="12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B88" s="5">
         <v>46091.66873747685</v>
@@ -6761,7 +6732,7 @@
         <v>46091.70105590278</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -6785,7 +6756,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6793,18 +6764,18 @@
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
       <c r="S88" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B89" s="8">
         <v>46091.66879239584</v>
@@ -6814,7 +6785,7 @@
         <v>46174.65693922454</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6841,13 +6812,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="Q89" s="8">
         <v>46105</v>
@@ -6862,12 +6833,12 @@
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B90" s="5">
         <v>46091.66899358796</v>
@@ -6877,7 +6848,7 @@
         <v>46157.198019421296</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6904,13 +6875,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="O90" s="6" t="s">
-        <v>305</v>
-      </c>
       <c r="P90" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q90" s="5">
         <v>46148</v>
@@ -6925,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="U90" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -2927,7 +2927,7 @@
         <v>46120.70601671297</v>
       </c>
       <c r="D26" s="5">
-        <v>46133.63083221065</v>
+        <v>46220.88597737269</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -3598,7 +3598,7 @@
         <v>46107.79872496528</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.79873737269</v>
+        <v>46220.93255427083</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -5747,7 +5747,7 @@
         <v>46161.91016861111</v>
       </c>
       <c r="D72" s="5">
-        <v>46161.91018041667</v>
+        <v>46222.566904629624</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="307">
   <si>
     <t>50001477- TRITON MINERA</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>propuesta nucleo  rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
@@ -2671,7 +2674,7 @@
         <v>46097.53080361111</v>
       </c>
       <c r="D22" s="5">
-        <v>46100.764148229166</v>
+        <v>46223.81979490741</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2680,9 +2683,11 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I22" s="5">
         <v>45978</v>
       </c>
@@ -2705,7 +2710,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>45978</v>
@@ -2725,7 +2730,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46073.66616008102</v>
@@ -2734,18 +2739,20 @@
         <v>46097.53074555556</v>
       </c>
       <c r="D23" s="8">
-        <v>46100.76426966435</v>
+        <v>46223.81979163195</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I23" s="8">
         <v>45978</v>
       </c>
@@ -2768,7 +2775,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>45978</v>
@@ -2788,7 +2795,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46076.66316038194</v>
@@ -2800,7 +2807,7 @@
         <v>46107.797543692126</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2833,7 +2840,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>45978</v>
@@ -2853,7 +2860,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46099.53305806713</v>
@@ -2865,7 +2872,7 @@
         <v>46133.6306462963</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2898,7 +2905,7 @@
         <v>69</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q25" s="8">
         <v>45978</v>
@@ -2918,7 +2925,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46073.66616042824</v>
@@ -2930,7 +2937,7 @@
         <v>46220.88597737269</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -2954,7 +2961,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -2967,7 +2974,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="8">
         <v>46073.66616130787</v>
@@ -2979,16 +2986,16 @@
         <v>46133.63077927083</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I27" s="8">
         <v>45973</v>
@@ -3006,13 +3013,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q27" s="8">
         <v>45973</v>
@@ -3032,7 +3039,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46073.66616162037</v>
@@ -3044,16 +3051,16 @@
         <v>46097.53140097222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I28" s="5">
         <v>45973</v>
@@ -3071,29 +3078,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46073.66616197917</v>
@@ -3105,16 +3112,16 @@
         <v>46107.80055459491</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I29" s="8">
         <v>45993</v>
@@ -3132,29 +3139,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46073.66616234954</v>
@@ -3166,16 +3173,16 @@
         <v>46107.80059462963</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I30" s="5">
         <v>45993</v>
@@ -3193,29 +3200,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46073.66616068287</v>
@@ -3227,16 +3234,16 @@
         <v>46097.531336203705</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I31" s="8">
         <v>45980</v>
@@ -3254,13 +3261,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q31" s="8">
         <v>45980</v>
@@ -3280,7 +3287,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46073.6661609838</v>
@@ -3292,16 +3299,16 @@
         <v>46099.5338058912</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I32" s="5">
         <v>45980</v>
@@ -3319,29 +3326,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46073.66616126157</v>
@@ -3353,16 +3360,16 @@
         <v>46097.53131167824</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I33" s="8">
         <v>45982</v>
@@ -3380,29 +3387,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46073.6661615162</v>
@@ -3414,16 +3421,16 @@
         <v>46120.66851498843</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I34" s="5">
         <v>45975</v>
@@ -3441,13 +3448,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q34" s="5">
         <v>45975</v>
@@ -3467,7 +3474,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46073.66616178241</v>
@@ -3479,16 +3486,16 @@
         <v>46097.53208754629</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I35" s="8">
         <v>45975</v>
@@ -3506,29 +3513,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46073.66616206018</v>
@@ -3540,16 +3547,16 @@
         <v>46120.66848849537</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I36" s="5">
         <v>45986</v>
@@ -3567,29 +3574,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46073.66616232639</v>
@@ -3601,16 +3608,16 @@
         <v>46220.93255427083</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I37" s="8">
         <v>45980</v>
@@ -3628,13 +3635,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q37" s="8">
         <v>45980</v>
@@ -3654,7 +3661,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46073.66616260417</v>
@@ -3666,16 +3673,16 @@
         <v>46107.798620173606</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I38" s="5">
         <v>45980</v>
@@ -3693,29 +3700,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46073.66616087963</v>
@@ -3727,16 +3734,16 @@
         <v>46107.79871178241</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I39" s="8">
         <v>45982</v>
@@ -3754,29 +3761,29 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46073.666162685186</v>
@@ -3788,16 +3795,16 @@
         <v>46098.682025243055</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>45980</v>
@@ -3815,13 +3822,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q40" s="5">
         <v>45980</v>
@@ -3841,7 +3848,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46073.66616299769</v>
@@ -3853,16 +3860,16 @@
         <v>46097.531550381944</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>45980</v>
@@ -3880,29 +3887,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46073.66616332176</v>
@@ -3914,16 +3921,16 @@
         <v>46098.68181796296</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I42" s="5">
         <v>46000</v>
@@ -3941,29 +3948,29 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46076.680800381946</v>
@@ -3975,16 +3982,16 @@
         <v>46107.80089184028</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I43" s="8">
         <v>45980</v>
@@ -4002,13 +4009,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q43" s="8">
         <v>45980</v>
@@ -4028,7 +4035,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46076.68351988426</v>
@@ -4040,16 +4047,16 @@
         <v>46107.79886152778</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I44" s="5">
         <v>45980</v>
@@ -4067,13 +4074,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="5">
         <v>45987</v>
@@ -4082,18 +4089,18 @@
         <v>46020</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46076.68374787037</v>
@@ -4105,16 +4112,16 @@
         <v>46107.80083771991</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I45" s="8">
         <v>46009</v>
@@ -4132,13 +4139,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="8">
         <v>46021</v>
@@ -4147,18 +4154,18 @@
         <v>46101</v>
       </c>
       <c r="S45" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T45" s="9">
         <v>0</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46099.5301296875</v>
@@ -4170,16 +4177,16 @@
         <v>46133.63092840278</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" s="5">
         <v>45980</v>
@@ -4197,10 +4204,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4223,7 +4230,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46099.53044444445</v>
@@ -4235,16 +4242,16 @@
         <v>46107.80117737269</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" s="8">
         <v>45980</v>
@@ -4262,13 +4269,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4278,7 +4285,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46099.53058535879</v>
@@ -4290,16 +4297,16 @@
         <v>46120.664316898146</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I48" s="5">
         <v>45982</v>
@@ -4317,13 +4324,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4333,7 +4340,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46099.84979115741</v>
@@ -4345,16 +4352,16 @@
         <v>46120.64216769676</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I49" s="8">
         <v>45980</v>
@@ -4372,7 +4379,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>26</v>
@@ -4388,7 +4395,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B50" s="5">
         <v>46099.84984650463</v>
@@ -4400,16 +4407,16 @@
         <v>46120.664625185185</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I50" s="5">
         <v>45980</v>
@@ -4427,7 +4434,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>26</v>
@@ -4443,7 +4450,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="8">
         <v>46099.85031037037</v>
@@ -4455,16 +4462,16 @@
         <v>46120.66463688658</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I51" s="8">
         <v>45980</v>
@@ -4482,13 +4489,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4498,7 +4505,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46099.53128005787</v>
@@ -4510,16 +4517,16 @@
         <v>46120.66432236111</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46098</v>
@@ -4537,13 +4544,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4553,7 +4560,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46073.66616363426</v>
@@ -4565,7 +4572,7 @@
         <v>46171.70102094907</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4589,7 +4596,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4606,7 +4613,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46073.66616400463</v>
@@ -4618,16 +4625,16 @@
         <v>46098.521133449074</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I54" s="5">
         <v>45978</v>
@@ -4645,13 +4652,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="5">
         <v>45978</v>
@@ -4671,7 +4678,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46073.666162152775</v>
@@ -4683,16 +4690,16 @@
         <v>46114.78779920139</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I55" s="8">
         <v>46031</v>
@@ -4710,13 +4717,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q55" s="8">
         <v>46031</v>
@@ -4736,7 +4743,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46091.66724454861</v>
@@ -4748,16 +4755,16 @@
         <v>46114.787913576394</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I56" s="5">
         <v>46038</v>
@@ -4775,13 +4782,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46038</v>
@@ -4801,7 +4808,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46091.66727622686</v>
@@ -4813,16 +4820,16 @@
         <v>46171.70101023148</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I57" s="8">
         <v>46126</v>
@@ -4840,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q57" s="8">
         <v>46126</v>
@@ -4866,7 +4873,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46073.666162615744</v>
@@ -4878,7 +4885,7 @@
         <v>46105.69845173611</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4902,7 +4909,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4919,7 +4926,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
         <v>46073.666163182876</v>
@@ -4931,16 +4938,16 @@
         <v>46098.6852078588</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I59" s="8">
         <v>46029</v>
@@ -4958,13 +4965,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="8">
         <v>46029</v>
@@ -4984,7 +4991,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46073.66616355324</v>
@@ -4996,16 +5003,16 @@
         <v>46105.76186741898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I60" s="5">
         <v>46031</v>
@@ -5023,13 +5030,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="5">
         <v>46031</v>
@@ -5049,7 +5056,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B61" s="8">
         <v>46073.66616390046</v>
@@ -5061,7 +5068,7 @@
         <v>46128.769275729166</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5085,7 +5092,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5102,7 +5109,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46073.66616421296</v>
@@ -5114,16 +5121,16 @@
         <v>46105.7624659838</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I62" s="5">
         <v>46035</v>
@@ -5141,13 +5148,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q62" s="5">
         <v>46035</v>
@@ -5167,7 +5174,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>46073.66616528935</v>
@@ -5179,16 +5186,16 @@
         <v>46128.76978145834</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I63" s="8">
         <v>46044</v>
@@ -5206,13 +5213,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q63" s="8">
         <v>46044</v>
@@ -5232,7 +5239,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46073.666165601855</v>
@@ -5244,16 +5251,16 @@
         <v>46128.76926512731</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I64" s="5">
         <v>46073</v>
@@ -5271,13 +5278,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46073</v>
@@ -5297,7 +5304,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B65" s="8">
         <v>46073.666165902774</v>
@@ -5309,7 +5316,7 @@
         <v>46129.56078046296</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5350,7 +5357,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B66" s="5">
         <v>46073.666160196764</v>
@@ -5362,16 +5369,16 @@
         <v>46121.20568130787</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I66" s="5">
         <v>46119</v>
@@ -5389,13 +5396,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46119</v>
@@ -5415,7 +5422,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B67" s="8">
         <v>46073.666159976856</v>
@@ -5427,16 +5434,16 @@
         <v>46113.82647306713</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I67" s="8">
         <v>46097</v>
@@ -5454,13 +5461,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67" s="8">
         <v>46097</v>
@@ -5480,7 +5487,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46073.66615966435</v>
@@ -5498,10 +5505,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I68" s="5">
         <v>46091</v>
@@ -5519,10 +5526,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>54</v>
@@ -5545,7 +5552,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B69" s="8">
         <v>46073.66616625</v>
@@ -5557,16 +5564,16 @@
         <v>46120.6692159838</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I69" s="8">
         <v>46031</v>
@@ -5584,13 +5591,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q69" s="8">
         <v>46031</v>
@@ -5610,7 +5617,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5">
         <v>46077.628692094906</v>
@@ -5622,16 +5629,16 @@
         <v>46120.669255810186</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I70" s="5">
         <v>46087</v>
@@ -5649,13 +5656,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q70" s="5">
         <v>46087</v>
@@ -5675,7 +5682,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B71" s="8">
         <v>46099.54289777778</v>
@@ -5687,16 +5694,16 @@
         <v>46126.84746914352</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5712,13 +5719,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q71" s="8">
         <v>46100</v>
@@ -5738,7 +5745,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46073.66616042824</v>
@@ -5750,7 +5757,7 @@
         <v>46222.566904629624</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5774,7 +5781,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5791,7 +5798,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B73" s="8">
         <v>46073.66616069444</v>
@@ -5800,18 +5807,20 @@
         <v>46133.63037300926</v>
       </c>
       <c r="D73" s="8">
-        <v>46133.6409821875</v>
+        <v>46223.81993915509</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I73" s="8">
         <v>46077</v>
       </c>
@@ -5828,13 +5837,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q73" s="8">
         <v>46077</v>
@@ -5854,7 +5863,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B74" s="5">
         <v>46073.666160925924</v>
@@ -5863,18 +5872,20 @@
         <v>46133.63107418982</v>
       </c>
       <c r="D74" s="5">
-        <v>46133.63108886574</v>
+        <v>46223.81993549768</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I74" s="5">
         <v>46121</v>
       </c>
@@ -5891,13 +5902,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q74" s="5">
         <v>46121</v>
@@ -5917,7 +5928,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B75" s="8">
         <v>46073.66616116898</v>
@@ -5926,18 +5937,20 @@
         <v>46133.6318684375</v>
       </c>
       <c r="D75" s="8">
-        <v>46133.824655324075</v>
+        <v>46223.81993199074</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I75" s="8">
         <v>46099</v>
       </c>
@@ -5954,13 +5967,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q75" s="8">
         <v>46099</v>
@@ -5980,7 +5993,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B76" s="5">
         <v>46073.66616142361</v>
@@ -5989,18 +6002,20 @@
         <v>46148.43735436343</v>
       </c>
       <c r="D76" s="5">
-        <v>46148.43737315972</v>
+        <v>46223.81992763889</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I76" s="5">
         <v>46101</v>
       </c>
@@ -6017,13 +6032,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q76" s="5">
         <v>46101</v>
@@ -6043,7 +6058,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B77" s="8">
         <v>46077.822625057874</v>
@@ -6052,18 +6067,20 @@
         <v>46133.63184909722</v>
       </c>
       <c r="D77" s="8">
-        <v>46133.631866979165</v>
+        <v>46223.81992415509</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I77" s="8">
         <v>46097</v>
       </c>
@@ -6080,13 +6097,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q77" s="8">
         <v>46097</v>
@@ -6106,7 +6123,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B78" s="5">
         <v>46073.66616163195</v>
@@ -6115,18 +6132,20 @@
         <v>46157.48051982639</v>
       </c>
       <c r="D78" s="5">
-        <v>46157.55991597222</v>
+        <v>46223.8199193287</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I78" s="5">
         <v>46125</v>
       </c>
@@ -6143,13 +6162,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q78" s="5">
         <v>46125</v>
@@ -6169,7 +6188,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B79" s="8">
         <v>46073.666161863424</v>
@@ -6178,18 +6197,20 @@
         <v>46161.91015064815</v>
       </c>
       <c r="D79" s="8">
-        <v>46174.65712613426</v>
+        <v>46223.81991386574</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I79" s="8">
         <v>46127</v>
       </c>
@@ -6206,13 +6227,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q79" s="8">
         <v>46127</v>
@@ -6232,7 +6253,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46073.66616018518</v>
@@ -6244,7 +6265,7 @@
         <v>46174.65703878472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6268,7 +6289,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6285,7 +6306,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="8">
         <v>46073.66616054398</v>
@@ -6297,7 +6318,7 @@
         <v>46174.65710859954</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6324,13 +6345,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="8">
         <v>46128</v>
@@ -6350,7 +6371,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46073.666160810186</v>
@@ -6362,7 +6383,7 @@
         <v>46174.657109120366</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6387,13 +6408,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q82" s="5">
         <v>46129</v>
@@ -6413,7 +6434,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46073.66616108797</v>
@@ -6425,16 +6446,16 @@
         <v>46174.657109618056</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I83" s="8">
         <v>46134</v>
@@ -6452,13 +6473,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="8">
         <v>46134</v>
@@ -6478,7 +6499,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46073.6661613426</v>
@@ -6490,16 +6511,16 @@
         <v>46174.65693560185</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I84" s="5">
         <v>46135</v>
@@ -6517,13 +6538,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q84" s="5">
         <v>46135</v>
@@ -6543,7 +6564,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46073.666161608795</v>
@@ -6553,7 +6574,7 @@
         <v>46091.70009597222</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6577,7 +6598,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6585,18 +6606,18 @@
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
       <c r="S85" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T85" s="9">
         <v>0</v>
       </c>
       <c r="U85" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46073.666161898145</v>
@@ -6606,16 +6627,16 @@
         <v>46174.65693865741</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I86" s="5">
         <v>46136</v>
@@ -6633,13 +6654,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q86" s="5">
         <v>46136</v>
@@ -6654,12 +6675,12 @@
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B87" s="8">
         <v>46073.6661622338</v>
@@ -6669,16 +6690,16 @@
         <v>46174.6569387037</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I87" s="8">
         <v>46136</v>
@@ -6696,13 +6717,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q87" s="8">
         <v>46136</v>
@@ -6717,12 +6738,12 @@
         <v>0</v>
       </c>
       <c r="U87" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B88" s="5">
         <v>46091.66873747685</v>
@@ -6732,7 +6753,7 @@
         <v>46091.70105590278</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -6756,7 +6777,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6764,18 +6785,18 @@
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
       <c r="S88" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B89" s="8">
         <v>46091.66879239584</v>
@@ -6785,7 +6806,7 @@
         <v>46174.65693922454</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6812,13 +6833,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q89" s="8">
         <v>46105</v>
@@ -6833,12 +6854,12 @@
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B90" s="5">
         <v>46091.66899358796</v>
@@ -6848,7 +6869,7 @@
         <v>46157.198019421296</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6875,13 +6896,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q90" s="5">
         <v>46148</v>
@@ -6896,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="U90" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="307">
   <si>
     <t>50001477- TRITON MINERA</t>
   </si>
@@ -6380,7 +6380,7 @@
         <v>46161.909470625</v>
       </c>
       <c r="D82" s="5">
-        <v>46174.657109120366</v>
+        <v>46223.83389392361</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>250</v>
@@ -6389,9 +6389,11 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I82" s="5">
         <v>46129</v>
       </c>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="308">
   <si>
     <t>50001477- TRITON MINERA</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>propuesta nucleo  rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2686,7 +2689,7 @@
         <v>89</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I22" s="5">
         <v>45978</v>
@@ -2710,7 +2713,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>45978</v>
@@ -2730,7 +2733,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46073.66616008102</v>
@@ -2742,7 +2745,7 @@
         <v>46223.81979163195</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2751,7 +2754,7 @@
         <v>89</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I23" s="8">
         <v>45978</v>
@@ -2775,7 +2778,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>45978</v>
@@ -2795,7 +2798,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46076.66316038194</v>
@@ -2807,7 +2810,7 @@
         <v>46107.797543692126</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2840,7 +2843,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>45978</v>
@@ -2860,7 +2863,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46099.53305806713</v>
@@ -2872,7 +2875,7 @@
         <v>46133.6306462963</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2905,7 +2908,7 @@
         <v>69</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q25" s="8">
         <v>45978</v>
@@ -2925,7 +2928,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46073.66616042824</v>
@@ -2937,7 +2940,7 @@
         <v>46220.88597737269</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -2961,7 +2964,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -2974,7 +2977,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="8">
         <v>46073.66616130787</v>
@@ -2986,16 +2989,16 @@
         <v>46133.63077927083</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I27" s="8">
         <v>45973</v>
@@ -3013,13 +3016,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="8">
         <v>45973</v>
@@ -3039,7 +3042,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46073.66616162037</v>
@@ -3051,16 +3054,16 @@
         <v>46097.53140097222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>45973</v>
@@ -3078,29 +3081,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46073.66616197917</v>
@@ -3112,16 +3115,16 @@
         <v>46107.80055459491</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I29" s="8">
         <v>45993</v>
@@ -3139,29 +3142,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46073.66616234954</v>
@@ -3173,16 +3176,16 @@
         <v>46107.80059462963</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I30" s="5">
         <v>45993</v>
@@ -3200,29 +3203,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46073.66616068287</v>
@@ -3234,16 +3237,16 @@
         <v>46097.531336203705</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I31" s="8">
         <v>45980</v>
@@ -3261,13 +3264,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q31" s="8">
         <v>45980</v>
@@ -3287,7 +3290,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46073.6661609838</v>
@@ -3299,16 +3302,16 @@
         <v>46099.5338058912</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I32" s="5">
         <v>45980</v>
@@ -3326,29 +3329,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46073.66616126157</v>
@@ -3360,16 +3363,16 @@
         <v>46097.53131167824</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I33" s="8">
         <v>45982</v>
@@ -3387,29 +3390,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46073.6661615162</v>
@@ -3421,16 +3424,16 @@
         <v>46120.66851498843</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I34" s="5">
         <v>45975</v>
@@ -3448,13 +3451,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q34" s="5">
         <v>45975</v>
@@ -3474,7 +3477,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46073.66616178241</v>
@@ -3486,16 +3489,16 @@
         <v>46097.53208754629</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I35" s="8">
         <v>45975</v>
@@ -3513,29 +3516,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46073.66616206018</v>
@@ -3547,16 +3550,16 @@
         <v>46120.66848849537</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I36" s="5">
         <v>45986</v>
@@ -3574,29 +3577,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46073.66616232639</v>
@@ -3608,16 +3611,16 @@
         <v>46220.93255427083</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I37" s="8">
         <v>45980</v>
@@ -3635,13 +3638,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q37" s="8">
         <v>45980</v>
@@ -3661,7 +3664,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46073.66616260417</v>
@@ -3673,16 +3676,16 @@
         <v>46107.798620173606</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I38" s="5">
         <v>45980</v>
@@ -3700,29 +3703,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46073.66616087963</v>
@@ -3734,16 +3737,16 @@
         <v>46107.79871178241</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I39" s="8">
         <v>45982</v>
@@ -3761,29 +3764,29 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46073.666162685186</v>
@@ -3795,16 +3798,16 @@
         <v>46098.682025243055</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>45980</v>
@@ -3822,13 +3825,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q40" s="5">
         <v>45980</v>
@@ -3848,7 +3851,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46073.66616299769</v>
@@ -3860,16 +3863,16 @@
         <v>46097.531550381944</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>45980</v>
@@ -3887,29 +3890,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46073.66616332176</v>
@@ -3921,16 +3924,16 @@
         <v>46098.68181796296</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I42" s="5">
         <v>46000</v>
@@ -3948,29 +3951,29 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46076.680800381946</v>
@@ -3982,16 +3985,16 @@
         <v>46107.80089184028</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I43" s="8">
         <v>45980</v>
@@ -4009,13 +4012,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q43" s="8">
         <v>45980</v>
@@ -4035,7 +4038,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46076.68351988426</v>
@@ -4047,16 +4050,16 @@
         <v>46107.79886152778</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I44" s="5">
         <v>45980</v>
@@ -4074,13 +4077,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="5">
         <v>45987</v>
@@ -4089,18 +4092,18 @@
         <v>46020</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46076.68374787037</v>
@@ -4112,16 +4115,16 @@
         <v>46107.80083771991</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I45" s="8">
         <v>46009</v>
@@ -4139,13 +4142,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="8">
         <v>46021</v>
@@ -4154,18 +4157,18 @@
         <v>46101</v>
       </c>
       <c r="S45" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T45" s="9">
         <v>0</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46099.5301296875</v>
@@ -4177,16 +4180,16 @@
         <v>46133.63092840278</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I46" s="5">
         <v>45980</v>
@@ -4204,10 +4207,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4230,7 +4233,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46099.53044444445</v>
@@ -4242,16 +4245,16 @@
         <v>46107.80117737269</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I47" s="8">
         <v>45980</v>
@@ -4269,13 +4272,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4285,7 +4288,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46099.53058535879</v>
@@ -4297,16 +4300,16 @@
         <v>46120.664316898146</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I48" s="5">
         <v>45982</v>
@@ -4324,13 +4327,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4340,7 +4343,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46099.84979115741</v>
@@ -4352,16 +4355,16 @@
         <v>46120.64216769676</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I49" s="8">
         <v>45980</v>
@@ -4379,7 +4382,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>26</v>
@@ -4395,7 +4398,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B50" s="5">
         <v>46099.84984650463</v>
@@ -4407,16 +4410,16 @@
         <v>46120.664625185185</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I50" s="5">
         <v>45980</v>
@@ -4434,7 +4437,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>26</v>
@@ -4450,7 +4453,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" s="8">
         <v>46099.85031037037</v>
@@ -4462,16 +4465,16 @@
         <v>46120.66463688658</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I51" s="8">
         <v>45980</v>
@@ -4489,13 +4492,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4505,7 +4508,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" s="5">
         <v>46099.53128005787</v>
@@ -4517,16 +4520,16 @@
         <v>46120.66432236111</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46098</v>
@@ -4544,13 +4547,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4560,7 +4563,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46073.66616363426</v>
@@ -4572,7 +4575,7 @@
         <v>46171.70102094907</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4596,7 +4599,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5">
         <v>46073.66616400463</v>
@@ -4625,16 +4628,16 @@
         <v>46098.521133449074</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I54" s="5">
         <v>45978</v>
@@ -4652,13 +4655,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q54" s="5">
         <v>45978</v>
@@ -4678,7 +4681,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B55" s="8">
         <v>46073.666162152775</v>
@@ -4690,16 +4693,16 @@
         <v>46114.78779920139</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I55" s="8">
         <v>46031</v>
@@ -4717,13 +4720,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="8">
         <v>46031</v>
@@ -4743,7 +4746,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46091.66724454861</v>
@@ -4755,16 +4758,16 @@
         <v>46114.787913576394</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I56" s="5">
         <v>46038</v>
@@ -4782,13 +4785,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46038</v>
@@ -4808,7 +4811,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46091.66727622686</v>
@@ -4820,16 +4823,16 @@
         <v>46171.70101023148</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I57" s="8">
         <v>46126</v>
@@ -4847,13 +4850,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="8">
         <v>46126</v>
@@ -4873,7 +4876,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46073.666162615744</v>
@@ -4885,7 +4888,7 @@
         <v>46105.69845173611</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4909,7 +4912,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4926,7 +4929,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="8">
         <v>46073.666163182876</v>
@@ -4938,16 +4941,16 @@
         <v>46098.6852078588</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I59" s="8">
         <v>46029</v>
@@ -4965,13 +4968,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="8">
         <v>46029</v>
@@ -4991,7 +4994,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46073.66616355324</v>
@@ -5003,16 +5006,16 @@
         <v>46105.76186741898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I60" s="5">
         <v>46031</v>
@@ -5030,13 +5033,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q60" s="5">
         <v>46031</v>
@@ -5056,7 +5059,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B61" s="8">
         <v>46073.66616390046</v>
@@ -5068,7 +5071,7 @@
         <v>46128.769275729166</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5092,7 +5095,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5109,7 +5112,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46073.66616421296</v>
@@ -5121,16 +5124,16 @@
         <v>46105.7624659838</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I62" s="5">
         <v>46035</v>
@@ -5148,13 +5151,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q62" s="5">
         <v>46035</v>
@@ -5174,7 +5177,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B63" s="8">
         <v>46073.66616528935</v>
@@ -5186,16 +5189,16 @@
         <v>46128.76978145834</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I63" s="8">
         <v>46044</v>
@@ -5213,13 +5216,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q63" s="8">
         <v>46044</v>
@@ -5239,7 +5242,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46073.666165601855</v>
@@ -5251,16 +5254,16 @@
         <v>46128.76926512731</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I64" s="5">
         <v>46073</v>
@@ -5278,13 +5281,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q64" s="5">
         <v>46073</v>
@@ -5304,7 +5307,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B65" s="8">
         <v>46073.666165902774</v>
@@ -5316,7 +5319,7 @@
         <v>46129.56078046296</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5357,7 +5360,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
         <v>46073.666160196764</v>
@@ -5369,16 +5372,16 @@
         <v>46121.20568130787</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I66" s="5">
         <v>46119</v>
@@ -5396,13 +5399,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46119</v>
@@ -5422,7 +5425,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46073.666159976856</v>
@@ -5434,16 +5437,16 @@
         <v>46113.82647306713</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I67" s="8">
         <v>46097</v>
@@ -5461,13 +5464,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q67" s="8">
         <v>46097</v>
@@ -5487,7 +5490,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46073.66615966435</v>
@@ -5505,10 +5508,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I68" s="5">
         <v>46091</v>
@@ -5526,10 +5529,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>54</v>
@@ -5552,7 +5555,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B69" s="8">
         <v>46073.66616625</v>
@@ -5564,16 +5567,16 @@
         <v>46120.6692159838</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I69" s="8">
         <v>46031</v>
@@ -5591,13 +5594,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q69" s="8">
         <v>46031</v>
@@ -5617,7 +5620,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B70" s="5">
         <v>46077.628692094906</v>
@@ -5629,16 +5632,16 @@
         <v>46120.669255810186</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I70" s="5">
         <v>46087</v>
@@ -5656,13 +5659,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q70" s="5">
         <v>46087</v>
@@ -5682,7 +5685,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B71" s="8">
         <v>46099.54289777778</v>
@@ -5694,16 +5697,16 @@
         <v>46126.84746914352</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="8">
@@ -5719,13 +5722,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q71" s="8">
         <v>46100</v>
@@ -5745,7 +5748,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46073.66616042824</v>
@@ -5757,7 +5760,7 @@
         <v>46222.566904629624</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5781,7 +5784,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5798,7 +5801,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B73" s="8">
         <v>46073.66616069444</v>
@@ -5810,7 +5813,7 @@
         <v>46223.81993915509</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5819,7 +5822,7 @@
         <v>89</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I73" s="8">
         <v>46077</v>
@@ -5837,13 +5840,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q73" s="8">
         <v>46077</v>
@@ -5863,7 +5866,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B74" s="5">
         <v>46073.666160925924</v>
@@ -5875,7 +5878,7 @@
         <v>46223.81993549768</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5884,7 +5887,7 @@
         <v>89</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I74" s="5">
         <v>46121</v>
@@ -5902,13 +5905,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q74" s="5">
         <v>46121</v>
@@ -5928,7 +5931,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B75" s="8">
         <v>46073.66616116898</v>
@@ -5940,7 +5943,7 @@
         <v>46223.81993199074</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5949,7 +5952,7 @@
         <v>89</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I75" s="8">
         <v>46099</v>
@@ -5967,13 +5970,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q75" s="8">
         <v>46099</v>
@@ -5993,7 +5996,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
         <v>46073.66616142361</v>
@@ -6005,7 +6008,7 @@
         <v>46223.81992763889</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6014,7 +6017,7 @@
         <v>89</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I76" s="5">
         <v>46101</v>
@@ -6032,13 +6035,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="5">
         <v>46101</v>
@@ -6058,7 +6061,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B77" s="8">
         <v>46077.822625057874</v>
@@ -6070,7 +6073,7 @@
         <v>46223.81992415509</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6079,7 +6082,7 @@
         <v>89</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I77" s="8">
         <v>46097</v>
@@ -6097,13 +6100,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q77" s="8">
         <v>46097</v>
@@ -6123,7 +6126,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B78" s="5">
         <v>46073.66616163195</v>
@@ -6135,7 +6138,7 @@
         <v>46223.8199193287</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6144,7 +6147,7 @@
         <v>89</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I78" s="5">
         <v>46125</v>
@@ -6162,13 +6165,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="5">
         <v>46125</v>
@@ -6188,7 +6191,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B79" s="8">
         <v>46073.666161863424</v>
@@ -6200,7 +6203,7 @@
         <v>46223.81991386574</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6209,7 +6212,7 @@
         <v>89</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I79" s="8">
         <v>46127</v>
@@ -6227,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q79" s="8">
         <v>46127</v>
@@ -6253,7 +6256,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46073.66616018518</v>
@@ -6265,7 +6268,7 @@
         <v>46174.65703878472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6289,7 +6292,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6306,7 +6309,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B81" s="8">
         <v>46073.66616054398</v>
@@ -6318,7 +6321,7 @@
         <v>46174.65710859954</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6345,13 +6348,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q81" s="8">
         <v>46128</v>
@@ -6371,7 +6374,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46073.666160810186</v>
@@ -6383,7 +6386,7 @@
         <v>46223.83389392361</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6392,7 +6395,7 @@
         <v>89</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I82" s="5">
         <v>46129</v>
@@ -6410,13 +6413,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q82" s="5">
         <v>46129</v>
@@ -6436,7 +6439,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
         <v>46073.66616108797</v>
@@ -6448,16 +6451,16 @@
         <v>46174.657109618056</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I83" s="8">
         <v>46134</v>
@@ -6475,13 +6478,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="8">
         <v>46134</v>
@@ -6501,7 +6504,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
         <v>46073.6661613426</v>
@@ -6513,16 +6516,16 @@
         <v>46174.65693560185</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I84" s="5">
         <v>46135</v>
@@ -6540,13 +6543,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q84" s="5">
         <v>46135</v>
@@ -6566,7 +6569,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
         <v>46073.666161608795</v>
@@ -6576,7 +6579,7 @@
         <v>46091.70009597222</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6600,7 +6603,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6608,18 +6611,18 @@
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
       <c r="S85" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T85" s="9">
         <v>0</v>
       </c>
       <c r="U85" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B86" s="5">
         <v>46073.666161898145</v>
@@ -6629,16 +6632,16 @@
         <v>46174.65693865741</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I86" s="5">
         <v>46136</v>
@@ -6656,13 +6659,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q86" s="5">
         <v>46136</v>
@@ -6677,12 +6680,12 @@
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B87" s="8">
         <v>46073.6661622338</v>
@@ -6692,16 +6695,16 @@
         <v>46174.6569387037</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I87" s="8">
         <v>46136</v>
@@ -6719,13 +6722,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q87" s="8">
         <v>46136</v>
@@ -6740,12 +6743,12 @@
         <v>0</v>
       </c>
       <c r="U87" s="12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B88" s="5">
         <v>46091.66873747685</v>
@@ -6755,7 +6758,7 @@
         <v>46091.70105590278</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -6779,7 +6782,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6787,18 +6790,18 @@
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
       <c r="S88" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B89" s="8">
         <v>46091.66879239584</v>
@@ -6808,7 +6811,7 @@
         <v>46174.65693922454</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6835,13 +6838,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q89" s="8">
         <v>46105</v>
@@ -6856,12 +6859,12 @@
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B90" s="5">
         <v>46091.66899358796</v>
@@ -6871,7 +6874,7 @@
         <v>46157.198019421296</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6898,13 +6901,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q90" s="5">
         <v>46148</v>
@@ -6919,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="U90" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -5316,7 +5316,7 @@
         <v>46120.66940356481</v>
       </c>
       <c r="D65" s="8">
-        <v>46129.56078046296</v>
+        <v>46229.20920046297</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>209</v>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -901,34 +901,34 @@
     <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
+    <t>1213379054536819</t>
+  </si>
+  <si>
+    <t>Costos</t>
+  </si>
+  <si>
+    <t>Despacho,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213595645393176</t>
+  </si>
+  <si>
+    <t>Puesta en Marcha</t>
+  </si>
+  <si>
+    <t>Instalación componentes,Pruebas Instalación de componentes</t>
+  </si>
+  <si>
+    <t>1213595645393178</t>
+  </si>
+  <si>
+    <t>Instalación componentes</t>
+  </si>
+  <si>
+    <t>Pruebas Instalación de componentes,Puesta en Marcha</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213379054536819</t>
-  </si>
-  <si>
-    <t>Costos</t>
-  </si>
-  <si>
-    <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213595645393176</t>
-  </si>
-  <si>
-    <t>Puesta en Marcha</t>
-  </si>
-  <si>
-    <t>Instalación componentes,Pruebas Instalación de componentes</t>
-  </si>
-  <si>
-    <t>1213595645393178</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t>Pruebas Instalación de componentes,Puesta en Marcha</t>
   </si>
   <si>
     <t>1213595645393180</t>
@@ -6574,9 +6574,11 @@
       <c r="B85" s="8">
         <v>46073.666161608795</v>
       </c>
-      <c r="C85" s="9"/>
+      <c r="C85" s="8">
+        <v>46232.66524534722</v>
+      </c>
       <c r="D85" s="8">
-        <v>46091.70009597222</v>
+        <v>46232.66525769676</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6614,10 +6616,10 @@
         <v>112</v>
       </c>
       <c r="T85" s="9">
-        <v>0</v>
-      </c>
-      <c r="U85" s="10" t="s">
-        <v>113</v>
+        <v>1</v>
+      </c>
+      <c r="U85" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6627,9 +6629,11 @@
       <c r="B86" s="5">
         <v>46073.666161898145</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46232.665221469906</v>
+      </c>
       <c r="D86" s="5">
-        <v>46174.65693865741</v>
+        <v>46232.665237685185</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>293</v>
@@ -6677,25 +6681,27 @@
         <v>32</v>
       </c>
       <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="12" t="s">
-        <v>296</v>
+        <v>1</v>
+      </c>
+      <c r="U86" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B87" s="8">
         <v>46073.6661622338</v>
       </c>
-      <c r="C87" s="9"/>
+      <c r="C87" s="8">
+        <v>46232.665228541664</v>
+      </c>
       <c r="D87" s="8">
-        <v>46174.6569387037</v>
+        <v>46232.66524636574</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6725,7 +6731,7 @@
         <v>290</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>290</v>
@@ -6740,15 +6746,15 @@
         <v>32</v>
       </c>
       <c r="T87" s="9">
-        <v>0</v>
-      </c>
-      <c r="U87" s="12" t="s">
-        <v>296</v>
+        <v>1</v>
+      </c>
+      <c r="U87" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B88" s="5">
         <v>46091.66873747685</v>
@@ -6758,7 +6764,7 @@
         <v>46091.70105590278</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -6782,7 +6788,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6801,7 +6807,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B89" s="8">
         <v>46091.66879239584</v>
@@ -6811,7 +6817,7 @@
         <v>46174.65693922454</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6838,13 +6844,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>287</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q89" s="8">
         <v>46105</v>
@@ -6859,7 +6865,7 @@
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6901,13 +6907,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q90" s="5">
         <v>46148</v>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="299">
   <si>
     <t>50001477- TRITON MINERA</t>
   </si>
@@ -877,7 +877,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Logistica:,Gestion,Costos,Instalación componentes</t>
+    <t>Logistica:,Gestion,Costos</t>
   </si>
   <si>
     <t>1213379054536817</t>
@@ -908,33 +908,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213595645393176</t>
-  </si>
-  <si>
-    <t>Puesta en Marcha</t>
-  </si>
-  <si>
-    <t>Instalación componentes,Pruebas Instalación de componentes</t>
-  </si>
-  <si>
-    <t>1213595645393178</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t>Pruebas Instalación de componentes,Puesta en Marcha</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213595645393180</t>
-  </si>
-  <si>
-    <t>Pruebas Instalación de componentes</t>
   </si>
 </sst>
 </file>
@@ -964,7 +937,7 @@
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1004,11 +977,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF62d26f"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1054,7 +1022,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1073,7 +1041,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1458,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U90"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -6513,7 +6480,7 @@
         <v>46174.656916736116</v>
       </c>
       <c r="D84" s="5">
-        <v>46174.65693560185</v>
+        <v>46240.714808125005</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6750,185 +6717,6 @@
       </c>
       <c r="U87" s="11" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B88" s="5">
-        <v>46091.66873747685</v>
-      </c>
-      <c r="C88" s="6"/>
-      <c r="D88" s="5">
-        <v>46091.70105590278</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B89" s="8">
-        <v>46091.66879239584</v>
-      </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="8">
-        <v>46174.65693922454</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I89" s="8">
-        <v>46136</v>
-      </c>
-      <c r="J89" s="8">
-        <v>46147</v>
-      </c>
-      <c r="K89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q89" s="8">
-        <v>46105</v>
-      </c>
-      <c r="R89" s="8">
-        <v>46147</v>
-      </c>
-      <c r="S89" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T89" s="9">
-        <v>0</v>
-      </c>
-      <c r="U89" s="12" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B90" s="5">
-        <v>46091.66899358796</v>
-      </c>
-      <c r="C90" s="6"/>
-      <c r="D90" s="5">
-        <v>46157.198019421296</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I90" s="5">
-        <v>46148</v>
-      </c>
-      <c r="J90" s="5">
-        <v>46156</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>46148</v>
-      </c>
-      <c r="R90" s="5">
-        <v>46156</v>
-      </c>
-      <c r="S90" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="10" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -1528,13 +1528,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.66615903935</v>
+        <v>46073.499492372684</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72419498843</v>
+        <v>46092.55752832176</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.530560405095</v>
+        <v>46097.363893738424</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1577,13 +1577,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.66615939815</v>
+        <v>46073.499492731484</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72416780093</v>
+        <v>46092.55750113426</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.87806965278</v>
+        <v>46133.71140298611</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1642,13 +1642,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.66615962963</v>
+        <v>46073.49949296296</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.724168298606</v>
+        <v>46092.55750163195</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.7241959838</v>
+        <v>46092.55752931713</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1707,13 +1707,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.66615988426</v>
+        <v>46073.49949321759</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.724168726854</v>
+        <v>46092.55750206018</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72419625</v>
+        <v>46092.55752958333</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1772,13 +1772,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.666160231485</v>
+        <v>46073.499493564814</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72416920139</v>
+        <v>46092.55750253472</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.76511025463</v>
+        <v>46100.598443587965</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1837,13 +1837,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.66616047454</v>
+        <v>46073.499493807874</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72416982639</v>
+        <v>46092.557503159725</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.7241962963</v>
+        <v>46092.55752962963</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1902,13 +1902,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.666160787034</v>
+        <v>46073.49949412037</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.60355960648</v>
+        <v>46129.43689293982</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.60357364583</v>
+        <v>46129.43690697917</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1955,13 +1955,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.66616105324</v>
+        <v>46073.499494386575</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.53196606482</v>
+        <v>46097.36529939815</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.53198291667</v>
+        <v>46097.36531625</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2020,13 +2020,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.66616129629</v>
+        <v>46073.49949462963</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.603544247686</v>
+        <v>46129.436877581014</v>
       </c>
       <c r="D12" s="5">
-        <v>46129.603824375</v>
+        <v>46129.43715770834</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2085,13 +2085,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.666161597226</v>
+        <v>46073.499494930555</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.53042917824</v>
+        <v>46097.36376251157</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.774145937496</v>
+        <v>46129.60747927084</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2134,13 +2134,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.66616013889</v>
+        <v>46073.49949347222</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.52783832176</v>
+        <v>46097.361171655095</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.527857037036</v>
+        <v>46097.36119037037</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2199,13 +2199,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.66616097222</v>
+        <v>46073.49949430556</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.53031609954</v>
+        <v>46097.36364943287</v>
       </c>
       <c r="D15" s="8">
-        <v>46100.76503991898</v>
+        <v>46100.59837325232</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2264,13 +2264,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.66616127315</v>
+        <v>46073.49949460648</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.52820017361</v>
+        <v>46097.36153350695</v>
       </c>
       <c r="D16" s="5">
-        <v>46100.765728252314</v>
+        <v>46100.59906158565</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2329,13 +2329,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.666161574074</v>
+        <v>46073.4994949074</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.53041068287</v>
+        <v>46097.3637440162</v>
       </c>
       <c r="D17" s="8">
-        <v>46133.6306210301</v>
+        <v>46133.463954363426</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2394,13 +2394,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.666161875</v>
+        <v>46073.499495208336</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.79754208333</v>
+        <v>46107.63087541667</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.63072813657</v>
+        <v>46133.46406146991</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2443,13 +2443,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.666162442125</v>
+        <v>46073.49949577547</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.5306434838</v>
+        <v>46097.36397681713</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.53065947916</v>
+        <v>46097.363992812505</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2508,13 +2508,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.66616216435</v>
+        <v>46073.49949549769</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.53069637732</v>
+        <v>46097.36402971065</v>
       </c>
       <c r="D20" s="5">
-        <v>46133.6306669676</v>
+        <v>46133.464000300926</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2573,13 +2573,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.66616271991</v>
+        <v>46073.49949605324</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.53204369213</v>
+        <v>46097.36537702546</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.53206203703</v>
+        <v>46097.36539537037</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2638,13 +2638,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.66616300926</v>
+        <v>46073.49949634259</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.53080361111</v>
+        <v>46097.364136944445</v>
       </c>
       <c r="D22" s="5">
-        <v>46223.81979490741</v>
+        <v>46223.65312824074</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2703,13 +2703,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.66616008102</v>
+        <v>46073.49949341435</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.53074555556</v>
+        <v>46097.36407888889</v>
       </c>
       <c r="D23" s="8">
-        <v>46223.81979163195</v>
+        <v>46223.653124965276</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2768,13 +2768,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46076.66316038194</v>
+        <v>46076.496493715276</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.797523402776</v>
+        <v>46107.63085673611</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.797543692126</v>
+        <v>46107.63087702546</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2833,13 +2833,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46099.53305806713</v>
+        <v>46099.366391400465</v>
       </c>
       <c r="C25" s="8">
-        <v>46099.53407392361</v>
+        <v>46099.36740725694</v>
       </c>
       <c r="D25" s="8">
-        <v>46133.6306462963</v>
+        <v>46133.463979629625</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2898,13 +2898,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.66616042824</v>
+        <v>46073.49949376157</v>
       </c>
       <c r="C26" s="5">
-        <v>46120.70601671297</v>
+        <v>46120.539350046296</v>
       </c>
       <c r="D26" s="5">
-        <v>46220.88597737269</v>
+        <v>46220.719310706016</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2947,13 +2947,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.66616130787</v>
+        <v>46073.499494641204</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.80060909722</v>
+        <v>46107.633942430555</v>
       </c>
       <c r="D27" s="8">
-        <v>46133.63077927083</v>
+        <v>46133.46411260417</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3012,13 +3012,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.66616162037</v>
+        <v>46073.49949495371</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.53139914352</v>
+        <v>46097.36473247685</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.53140097222</v>
+        <v>46097.364734305556</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3073,13 +3073,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.66616197917</v>
+        <v>46073.4994953125</v>
       </c>
       <c r="C29" s="8">
-        <v>46107.80055341435</v>
+        <v>46107.63388674769</v>
       </c>
       <c r="D29" s="8">
-        <v>46107.80055459491</v>
+        <v>46107.63388792824</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3134,13 +3134,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.66616234954</v>
+        <v>46073.499495682874</v>
       </c>
       <c r="C30" s="5">
-        <v>46107.80059315972</v>
+        <v>46107.63392649306</v>
       </c>
       <c r="D30" s="5">
-        <v>46107.80059462963</v>
+        <v>46107.63392796296</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3195,13 +3195,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.66616068287</v>
+        <v>46073.4994940162</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.53132358796</v>
+        <v>46097.3646569213</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.531336203705</v>
+        <v>46097.36466953704</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3260,13 +3260,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.6661609838</v>
+        <v>46073.49949431713</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.53127260417</v>
+        <v>46097.3646059375</v>
       </c>
       <c r="D32" s="5">
-        <v>46099.5338058912</v>
+        <v>46099.36713922454</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3321,13 +3321,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.66616126157</v>
+        <v>46073.49949459491</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.53131013889</v>
+        <v>46097.36464347222</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.53131167824</v>
+        <v>46097.36464501158</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3382,13 +3382,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.6661615162</v>
+        <v>46073.49949484954</v>
       </c>
       <c r="C34" s="5">
-        <v>46120.668502002314</v>
+        <v>46120.50183533565</v>
       </c>
       <c r="D34" s="5">
-        <v>46120.66851498843</v>
+        <v>46120.50184832176</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3447,13 +3447,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.66616178241</v>
+        <v>46073.49949511574</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.53208601852</v>
+        <v>46097.36541935185</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.53208754629</v>
+        <v>46097.36542087963</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3508,13 +3508,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.66616206018</v>
+        <v>46073.499495393524</v>
       </c>
       <c r="C36" s="5">
-        <v>46120.668486828705</v>
+        <v>46120.50182016204</v>
       </c>
       <c r="D36" s="5">
-        <v>46120.66848849537</v>
+        <v>46120.5018218287</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3569,13 +3569,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.66616232639</v>
+        <v>46073.49949565972</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.79872496528</v>
+        <v>46107.63205829861</v>
       </c>
       <c r="D37" s="8">
-        <v>46220.93255427083</v>
+        <v>46220.76588760417</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3634,13 +3634,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.66616260417</v>
+        <v>46073.4994959375</v>
       </c>
       <c r="C38" s="5">
-        <v>46107.79861873842</v>
+        <v>46107.63195207176</v>
       </c>
       <c r="D38" s="5">
-        <v>46107.798620173606</v>
+        <v>46107.63195350695</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3695,13 +3695,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.66616087963</v>
+        <v>46073.49949421296</v>
       </c>
       <c r="C39" s="8">
-        <v>46107.798710462965</v>
+        <v>46107.6320437963</v>
       </c>
       <c r="D39" s="8">
-        <v>46107.79871178241</v>
+        <v>46107.63204511574</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3756,13 +3756,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.666162685186</v>
+        <v>46073.499496018514</v>
       </c>
       <c r="C40" s="5">
-        <v>46098.681831608796</v>
+        <v>46098.51516494213</v>
       </c>
       <c r="D40" s="5">
-        <v>46098.682025243055</v>
+        <v>46098.51535857639</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3821,13 +3821,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.66616299769</v>
+        <v>46073.49949633102</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.531549004634</v>
+        <v>46097.36488233796</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.531550381944</v>
+        <v>46097.36488371528</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3882,13 +3882,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.66616332176</v>
+        <v>46073.49949665509</v>
       </c>
       <c r="C42" s="5">
-        <v>46098.68181620371</v>
+        <v>46098.51514953704</v>
       </c>
       <c r="D42" s="5">
-        <v>46098.68181796296</v>
+        <v>46098.51515129629</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3943,13 +3943,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.680800381946</v>
+        <v>46076.514133715275</v>
       </c>
       <c r="C43" s="8">
-        <v>46107.80085251157</v>
+        <v>46107.63418584491</v>
       </c>
       <c r="D43" s="8">
-        <v>46107.80089184028</v>
+        <v>46107.634225173606</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4008,13 +4008,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.68351988426</v>
+        <v>46076.51685321759</v>
       </c>
       <c r="C44" s="5">
-        <v>46107.79885972222</v>
+        <v>46107.63219305556</v>
       </c>
       <c r="D44" s="5">
-        <v>46107.79886152778</v>
+        <v>46107.632194861115</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4073,13 +4073,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46076.68374787037</v>
+        <v>46076.5170812037</v>
       </c>
       <c r="C45" s="8">
-        <v>46107.80083613426</v>
+        <v>46107.634169467594</v>
       </c>
       <c r="D45" s="8">
-        <v>46107.80083771991</v>
+        <v>46107.63417105324</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4138,13 +4138,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46099.5301296875</v>
+        <v>46099.36346302083</v>
       </c>
       <c r="C46" s="5">
-        <v>46120.66386724537</v>
+        <v>46120.4972005787</v>
       </c>
       <c r="D46" s="5">
-        <v>46133.63092840278</v>
+        <v>46133.46426173611</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4203,13 +4203,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46099.53044444445</v>
+        <v>46099.36377777778</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.80117576389</v>
+        <v>46107.63450909722</v>
       </c>
       <c r="D47" s="8">
-        <v>46107.80117737269</v>
+        <v>46107.63451070602</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>100</v>
@@ -4258,13 +4258,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46099.53058535879</v>
+        <v>46099.36391869213</v>
       </c>
       <c r="C48" s="5">
-        <v>46120.664315358794</v>
+        <v>46120.49764869213</v>
       </c>
       <c r="D48" s="5">
-        <v>46120.664316898146</v>
+        <v>46120.49765023148</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>168</v>
@@ -4313,13 +4313,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46099.84979115741</v>
+        <v>46099.68312449074</v>
       </c>
       <c r="C49" s="8">
-        <v>46105.754452037036</v>
+        <v>46105.58778537037</v>
       </c>
       <c r="D49" s="8">
-        <v>46120.64216769676</v>
+        <v>46120.475501030094</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4368,13 +4368,13 @@
         <v>178</v>
       </c>
       <c r="B50" s="5">
-        <v>46099.84984650463</v>
+        <v>46099.683179837964</v>
       </c>
       <c r="C50" s="5">
-        <v>46120.66462393518</v>
+        <v>46120.49795726852</v>
       </c>
       <c r="D50" s="5">
-        <v>46120.664625185185</v>
+        <v>46120.49795851852</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>179</v>
@@ -4423,13 +4423,13 @@
         <v>180</v>
       </c>
       <c r="B51" s="8">
-        <v>46099.85031037037</v>
+        <v>46099.683643703705</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.66463579861</v>
+        <v>46120.497969131946</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.66463688658</v>
+        <v>46120.497970219905</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>181</v>
@@ -4478,13 +4478,13 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46099.53128005787</v>
+        <v>46099.364613391204</v>
       </c>
       <c r="C52" s="5">
-        <v>46120.64085998843</v>
+        <v>46120.47419332176</v>
       </c>
       <c r="D52" s="5">
-        <v>46120.66432236111</v>
+        <v>46120.497655694446</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -4533,13 +4533,13 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.66616363426</v>
+        <v>46073.49949696759</v>
       </c>
       <c r="C53" s="8">
-        <v>46171.70100961806</v>
+        <v>46171.53434295139</v>
       </c>
       <c r="D53" s="8">
-        <v>46171.70102094907</v>
+        <v>46171.53435428241</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>188</v>
@@ -4586,13 +4586,13 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.66616400463</v>
+        <v>46073.499497337965</v>
       </c>
       <c r="C54" s="5">
-        <v>46098.52111122685</v>
+        <v>46098.35444456019</v>
       </c>
       <c r="D54" s="5">
-        <v>46098.521133449074</v>
+        <v>46098.3544667824</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -4651,13 +4651,13 @@
         <v>195</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.666162152775</v>
+        <v>46073.49949548611</v>
       </c>
       <c r="C55" s="8">
-        <v>46114.787797592595</v>
+        <v>46114.62113092592</v>
       </c>
       <c r="D55" s="8">
-        <v>46114.78779920139</v>
+        <v>46114.621132534725</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>196</v>
@@ -4716,13 +4716,13 @@
         <v>199</v>
       </c>
       <c r="B56" s="5">
-        <v>46091.66724454861</v>
+        <v>46091.50057788195</v>
       </c>
       <c r="C56" s="5">
-        <v>46114.78789839121</v>
+        <v>46114.62123172454</v>
       </c>
       <c r="D56" s="5">
-        <v>46114.787913576394</v>
+        <v>46114.62124690972</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -4781,13 +4781,13 @@
         <v>202</v>
       </c>
       <c r="B57" s="8">
-        <v>46091.66727622686</v>
+        <v>46091.500609560186</v>
       </c>
       <c r="C57" s="8">
-        <v>46171.70098944445</v>
+        <v>46171.53432277778</v>
       </c>
       <c r="D57" s="8">
-        <v>46171.70101023148</v>
+        <v>46171.53434356481</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>203</v>
@@ -4846,13 +4846,13 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.666162615744</v>
+        <v>46073.49949594907</v>
       </c>
       <c r="C58" s="5">
-        <v>46105.6984371875</v>
+        <v>46105.53177052083</v>
       </c>
       <c r="D58" s="5">
-        <v>46105.69845173611</v>
+        <v>46105.53178506944</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -4899,13 +4899,13 @@
         <v>211</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.666163182876</v>
+        <v>46073.499496516204</v>
       </c>
       <c r="C59" s="8">
-        <v>46098.68519152778</v>
+        <v>46098.51852486111</v>
       </c>
       <c r="D59" s="8">
-        <v>46098.6852078588</v>
+        <v>46098.51854119213</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>212</v>
@@ -4964,13 +4964,13 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.66616355324</v>
+        <v>46073.49949688658</v>
       </c>
       <c r="C60" s="5">
-        <v>46105.69841752315</v>
+        <v>46105.53175085648</v>
       </c>
       <c r="D60" s="5">
-        <v>46105.76186741898</v>
+        <v>46105.595200752316</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5029,13 +5029,13 @@
         <v>219</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.66616390046</v>
+        <v>46073.499497233795</v>
       </c>
       <c r="C61" s="8">
-        <v>46128.76926414351</v>
+        <v>46128.602597476856</v>
       </c>
       <c r="D61" s="8">
-        <v>46128.769275729166</v>
+        <v>46128.602609062495</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>220</v>
@@ -5082,13 +5082,13 @@
         <v>222</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.66616421296</v>
+        <v>46073.4994975463</v>
       </c>
       <c r="C62" s="5">
-        <v>46105.76245009259</v>
+        <v>46105.595783425924</v>
       </c>
       <c r="D62" s="5">
-        <v>46105.7624659838</v>
+        <v>46105.59579931713</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>223</v>
@@ -5147,13 +5147,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.66616528935</v>
+        <v>46073.49949862268</v>
       </c>
       <c r="C63" s="8">
-        <v>46128.493564386576</v>
+        <v>46128.326897719904</v>
       </c>
       <c r="D63" s="8">
-        <v>46128.76978145834</v>
+        <v>46128.603114791666</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>228</v>
@@ -5212,13 +5212,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.666165601855</v>
+        <v>46073.49949893518</v>
       </c>
       <c r="C64" s="5">
-        <v>46128.769248125</v>
+        <v>46128.60258145833</v>
       </c>
       <c r="D64" s="5">
-        <v>46128.76926512731</v>
+        <v>46128.60259846065</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5277,13 +5277,13 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.666165902774</v>
+        <v>46073.49949923611</v>
       </c>
       <c r="C65" s="8">
-        <v>46120.66940356481</v>
+        <v>46120.50273689815</v>
       </c>
       <c r="D65" s="8">
-        <v>46229.20920046297</v>
+        <v>46229.042533796295</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>209</v>
@@ -5330,13 +5330,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.666160196764</v>
+        <v>46073.49949353009</v>
       </c>
       <c r="C66" s="5">
-        <v>46113.826448865744</v>
+        <v>46113.65978219907</v>
       </c>
       <c r="D66" s="5">
-        <v>46121.20568130787</v>
+        <v>46121.0390146412</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5395,13 +5395,13 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.666159976856</v>
+        <v>46073.499493310184</v>
       </c>
       <c r="C67" s="8">
-        <v>46113.82647137731</v>
+        <v>46113.65980471065</v>
       </c>
       <c r="D67" s="8">
-        <v>46113.82647306713</v>
+        <v>46113.659806400465</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5460,13 +5460,13 @@
         <v>242</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.66615966435</v>
+        <v>46073.49949299768</v>
       </c>
       <c r="C68" s="5">
-        <v>46120.66859381944</v>
+        <v>46120.50192715278</v>
       </c>
       <c r="D68" s="5">
-        <v>46120.668609733795</v>
+        <v>46120.50194306713</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>55</v>
@@ -5525,13 +5525,13 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.66616625</v>
+        <v>46073.49949958333</v>
       </c>
       <c r="C69" s="8">
-        <v>46120.66919969907</v>
+        <v>46120.502533032406</v>
       </c>
       <c r="D69" s="8">
-        <v>46120.6692159838</v>
+        <v>46120.50254931713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5590,13 +5590,13 @@
         <v>246</v>
       </c>
       <c r="B70" s="5">
-        <v>46077.628692094906</v>
+        <v>46077.46202542824</v>
       </c>
       <c r="C70" s="5">
-        <v>46120.66924116898</v>
+        <v>46120.502574502316</v>
       </c>
       <c r="D70" s="5">
-        <v>46120.669255810186</v>
+        <v>46120.50258914352</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>247</v>
@@ -5655,13 +5655,13 @@
         <v>249</v>
       </c>
       <c r="B71" s="8">
-        <v>46099.54289777778</v>
+        <v>46099.376231111106</v>
       </c>
       <c r="C71" s="8">
-        <v>46126.8474675</v>
+        <v>46126.68080083333</v>
       </c>
       <c r="D71" s="8">
-        <v>46126.84746914352</v>
+        <v>46126.680802476854</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>250</v>
@@ -5718,13 +5718,13 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.66616042824</v>
+        <v>46073.49949376157</v>
       </c>
       <c r="C72" s="5">
-        <v>46161.91016861111</v>
+        <v>46161.743501944446</v>
       </c>
       <c r="D72" s="5">
-        <v>46222.566904629624</v>
+        <v>46222.40023796297</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5771,13 +5771,13 @@
         <v>255</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.66616069444</v>
+        <v>46073.49949402778</v>
       </c>
       <c r="C73" s="8">
-        <v>46133.63037300926</v>
+        <v>46133.46370634259</v>
       </c>
       <c r="D73" s="8">
-        <v>46223.81993915509</v>
+        <v>46223.65327248843</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>256</v>
@@ -5836,13 +5836,13 @@
         <v>258</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.666160925924</v>
+        <v>46073.49949425926</v>
       </c>
       <c r="C74" s="5">
-        <v>46133.63107418982</v>
+        <v>46133.46440752315</v>
       </c>
       <c r="D74" s="5">
-        <v>46223.81993549768</v>
+        <v>46223.65326883102</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>238</v>
@@ -5901,13 +5901,13 @@
         <v>261</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.66616116898</v>
+        <v>46073.49949450231</v>
       </c>
       <c r="C75" s="8">
-        <v>46133.6318684375</v>
+        <v>46133.46520177083</v>
       </c>
       <c r="D75" s="8">
-        <v>46223.81993199074</v>
+        <v>46223.65326532407</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>241</v>
@@ -5966,13 +5966,13 @@
         <v>264</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.66616142361</v>
+        <v>46073.49949475694</v>
       </c>
       <c r="C76" s="5">
-        <v>46148.43735436343</v>
+        <v>46148.27068769676</v>
       </c>
       <c r="D76" s="5">
-        <v>46223.81992763889</v>
+        <v>46223.65326097222</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>245</v>
@@ -6031,13 +6031,13 @@
         <v>266</v>
       </c>
       <c r="B77" s="8">
-        <v>46077.822625057874</v>
+        <v>46077.6559583912</v>
       </c>
       <c r="C77" s="8">
-        <v>46133.63184909722</v>
+        <v>46133.465182430555</v>
       </c>
       <c r="D77" s="8">
-        <v>46223.81992415509</v>
+        <v>46223.653257488426</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>248</v>
@@ -6096,13 +6096,13 @@
         <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.66616163195</v>
+        <v>46073.499494965276</v>
       </c>
       <c r="C78" s="5">
-        <v>46157.48051982639</v>
+        <v>46157.31385315972</v>
       </c>
       <c r="D78" s="5">
-        <v>46223.8199193287</v>
+        <v>46223.653252662036</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>206</v>
@@ -6161,13 +6161,13 @@
         <v>271</v>
       </c>
       <c r="B79" s="8">
-        <v>46073.666161863424</v>
+        <v>46073.49949519676</v>
       </c>
       <c r="C79" s="8">
-        <v>46161.91015064815</v>
+        <v>46161.74348398148</v>
       </c>
       <c r="D79" s="8">
-        <v>46223.81991386574</v>
+        <v>46223.65324719908</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>272</v>
@@ -6226,13 +6226,13 @@
         <v>274</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.66616018518</v>
+        <v>46073.49949351852</v>
       </c>
       <c r="C80" s="5">
-        <v>46174.65693556713</v>
+        <v>46174.49026890047</v>
       </c>
       <c r="D80" s="5">
-        <v>46174.65703878472</v>
+        <v>46174.49037211806</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>275</v>
@@ -6279,13 +6279,13 @@
         <v>277</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.66616054398</v>
+        <v>46073.499493877316</v>
       </c>
       <c r="C81" s="8">
-        <v>46161.909525219904</v>
+        <v>46161.74285855324</v>
       </c>
       <c r="D81" s="8">
-        <v>46174.65710859954</v>
+        <v>46174.49044193287</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6344,13 +6344,13 @@
         <v>280</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.666160810186</v>
+        <v>46073.499494143514</v>
       </c>
       <c r="C82" s="5">
-        <v>46161.909470625</v>
+        <v>46161.74280395833</v>
       </c>
       <c r="D82" s="5">
-        <v>46223.83389392361</v>
+        <v>46223.66722725694</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>251</v>
@@ -6409,13 +6409,13 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.66616108797</v>
+        <v>46073.499494421296</v>
       </c>
       <c r="C83" s="8">
-        <v>46142.928979212964</v>
+        <v>46142.7623125463</v>
       </c>
       <c r="D83" s="8">
-        <v>46174.657109618056</v>
+        <v>46174.490442951384</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>284</v>
@@ -6474,13 +6474,13 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.6661613426</v>
+        <v>46073.499494675925</v>
       </c>
       <c r="C84" s="5">
-        <v>46174.656916736116</v>
+        <v>46174.490250069444</v>
       </c>
       <c r="D84" s="5">
-        <v>46240.714808125005</v>
+        <v>46240.548141458334</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6539,13 +6539,13 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46073.666161608795</v>
+        <v>46073.49949494213</v>
       </c>
       <c r="C85" s="8">
-        <v>46232.66524534722</v>
+        <v>46232.498578680556</v>
       </c>
       <c r="D85" s="8">
-        <v>46232.66525769676</v>
+        <v>46232.49859103009</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6594,13 +6594,13 @@
         <v>292</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.666161898145</v>
+        <v>46073.49949523148</v>
       </c>
       <c r="C86" s="5">
-        <v>46232.665221469906</v>
+        <v>46232.49855480324</v>
       </c>
       <c r="D86" s="5">
-        <v>46232.665237685185</v>
+        <v>46232.498571018514</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>293</v>
@@ -6659,13 +6659,13 @@
         <v>296</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.6661622338</v>
+        <v>46073.49949556713</v>
       </c>
       <c r="C87" s="8">
-        <v>46232.665228541664</v>
+        <v>46232.498561875</v>
       </c>
       <c r="D87" s="8">
-        <v>46232.66524636574</v>
+        <v>46232.49857969907</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>297</v>

--- a/data/50001477 - TRITON MINERA.xlsx
+++ b/data/50001477 - TRITON MINERA.xlsx
@@ -1528,13 +1528,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.499492372684</v>
+        <v>46073.66615903935</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55752832176</v>
+        <v>46092.72419498843</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.363893738424</v>
+        <v>46097.530560405095</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1577,13 +1577,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.499492731484</v>
+        <v>46073.66615939815</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55750113426</v>
+        <v>46092.72416780093</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71140298611</v>
+        <v>46133.87806965278</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1642,13 +1642,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.49949296296</v>
+        <v>46073.66615962963</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55750163195</v>
+        <v>46092.724168298606</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55752931713</v>
+        <v>46092.7241959838</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1707,13 +1707,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.49949321759</v>
+        <v>46073.66615988426</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55750206018</v>
+        <v>46092.724168726854</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55752958333</v>
+        <v>46092.72419625</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1772,13 +1772,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.499493564814</v>
+        <v>46073.666160231485</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55750253472</v>
+        <v>46092.72416920139</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.598443587965</v>
+        <v>46100.76511025463</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1837,13 +1837,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.499493807874</v>
+        <v>46073.66616047454</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.557503159725</v>
+        <v>46092.72416982639</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55752962963</v>
+        <v>46092.7241962963</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1902,13 +1902,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.49949412037</v>
+        <v>46073.666160787034</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.43689293982</v>
+        <v>46129.60355960648</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.43690697917</v>
+        <v>46129.60357364583</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1955,13 +1955,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.499494386575</v>
+        <v>46073.66616105324</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.36529939815</v>
+        <v>46097.53196606482</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.36531625</v>
+        <v>46097.53198291667</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2020,13 +2020,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.49949462963</v>
+        <v>46073.66616129629</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.436877581014</v>
+        <v>46129.603544247686</v>
       </c>
       <c r="D12" s="5">
-        <v>46129.43715770834</v>
+        <v>46129.603824375</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2085,13 +2085,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.499494930555</v>
+        <v>46073.666161597226</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.36376251157</v>
+        <v>46097.53042917824</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.60747927084</v>
+        <v>46129.774145937496</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2134,13 +2134,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.49949347222</v>
+        <v>46073.66616013889</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.361171655095</v>
+        <v>46097.52783832176</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.36119037037</v>
+        <v>46097.527857037036</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2199,13 +2199,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.49949430556</v>
+        <v>46073.66616097222</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.36364943287</v>
+        <v>46097.53031609954</v>
       </c>
       <c r="D15" s="8">
-        <v>46100.59837325232</v>
+        <v>46100.76503991898</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2264,13 +2264,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.49949460648</v>
+        <v>46073.66616127315</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.36153350695</v>
+        <v>46097.52820017361</v>
       </c>
       <c r="D16" s="5">
-        <v>46100.59906158565</v>
+        <v>46100.765728252314</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2329,13 +2329,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.4994949074</v>
+        <v>46073.666161574074</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.3637440162</v>
+        <v>46097.53041068287</v>
       </c>
       <c r="D17" s="8">
-        <v>46133.463954363426</v>
+        <v>46133.6306210301</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2394,13 +2394,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.499495208336</v>
+        <v>46073.666161875</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.63087541667</v>
+        <v>46107.79754208333</v>
       </c>
       <c r="D18" s="5">
-        <v>46133.46406146991</v>
+        <v>46133.63072813657</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2443,13 +2443,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.49949577547</v>
+        <v>46073.666162442125</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.36397681713</v>
+        <v>46097.5306434838</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.363992812505</v>
+        <v>46097.53065947916</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2508,13 +2508,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.49949549769</v>
+        <v>46073.66616216435</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.36402971065</v>
+        <v>46097.53069637732</v>
       </c>
       <c r="D20" s="5">
-        <v>46133.464000300926</v>
+        <v>46133.6306669676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2573,13 +2573,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.49949605324</v>
+        <v>46073.66616271991</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.36537702546</v>
+        <v>46097.53204369213</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.36539537037</v>
+        <v>46097.53206203703</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2638,13 +2638,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.49949634259</v>
+        <v>46073.66616300926</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.364136944445</v>
+        <v>46097.53080361111</v>
       </c>
       <c r="D22" s="5">
-        <v>46223.65312824074</v>
+        <v>46223.81979490741</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2703,13 +2703,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.49949341435</v>
+        <v>46073.66616008102</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.36407888889</v>
+        <v>46097.53074555556</v>
       </c>
       <c r="D23" s="8">
-        <v>46223.653124965276</v>
+        <v>46223.81979163195</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2768,13 +2768,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46076.496493715276</v>
+        <v>46076.66316038194</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.63085673611</v>
+        <v>46107.797523402776</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.63087702546</v>
+        <v>46107.797543692126</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2833,13 +2833,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46099.366391400465</v>
+        <v>46099.53305806713</v>
       </c>
       <c r="C25" s="8">
-        <v>46099.36740725694</v>
+        <v>46099.53407392361</v>
       </c>
       <c r="D25" s="8">
-        <v>46133.463979629625</v>
+        <v>46133.6306462963</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2898,13 +2898,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.49949376157</v>
+        <v>46073.66616042824</v>
       </c>
       <c r="C26" s="5">
-        <v>46120.539350046296</v>
+        <v>46120.70601671297</v>
       </c>
       <c r="D26" s="5">
-        <v>46220.719310706016</v>
+        <v>46220.88597737269</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2947,13 +2947,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.499494641204</v>
+        <v>46073.66616130787</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.633942430555</v>
+        <v>46107.80060909722</v>
       </c>
       <c r="D27" s="8">
-        <v>46133.46411260417</v>
+        <v>46133.63077927083</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3012,13 +3012,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.49949495371</v>
+        <v>46073.66616162037</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.36473247685</v>
+        <v>46097.53139914352</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.364734305556</v>
+        <v>46097.53140097222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -3073,13 +3073,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.4994953125</v>
+        <v>46073.66616197917</v>
       </c>
       <c r="C29" s="8">
-        <v>46107.63388674769</v>
+        <v>46107.80055341435</v>
       </c>
       <c r="D29" s="8">
-        <v>46107.63388792824</v>
+        <v>46107.80055459491</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3134,13 +3134,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.499495682874</v>
+        <v>46073.66616234954</v>
       </c>
       <c r="C30" s="5">
-        <v>46107.63392649306</v>
+        <v>46107.80059315972</v>
       </c>
       <c r="D30" s="5">
-        <v>46107.63392796296</v>
+        <v>46107.80059462963</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3195,13 +3195,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.4994940162</v>
+        <v>46073.66616068287</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.3646569213</v>
+        <v>46097.53132358796</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.36466953704</v>
+        <v>46097.531336203705</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3260,13 +3260,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.49949431713</v>
+        <v>46073.6661609838</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.3646059375</v>
+        <v>46097.53127260417</v>
       </c>
       <c r="D32" s="5">
-        <v>46099.36713922454</v>
+        <v>46099.5338058912</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3321,13 +3321,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.49949459491</v>
+        <v>46073.66616126157</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.36464347222</v>
+        <v>46097.53131013889</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.36464501158</v>
+        <v>46097.53131167824</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3382,13 +3382,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.49949484954</v>
+        <v>46073.6661615162</v>
       </c>
       <c r="C34" s="5">
-        <v>46120.50183533565</v>
+        <v>46120.668502002314</v>
       </c>
       <c r="D34" s="5">
-        <v>46120.50184832176</v>
+        <v>46120.66851498843</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3447,13 +3447,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.49949511574</v>
+        <v>46073.66616178241</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.36541935185</v>
+        <v>46097.53208601852</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.36542087963</v>
+        <v>46097.53208754629</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3508,13 +3508,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.499495393524</v>
+        <v>46073.66616206018</v>
       </c>
       <c r="C36" s="5">
-        <v>46120.50182016204</v>
+        <v>46120.668486828705</v>
       </c>
       <c r="D36" s="5">
-        <v>46120.5018218287</v>
+        <v>46120.66848849537</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3569,13 +3569,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.49949565972</v>
+        <v>46073.66616232639</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.63205829861</v>
+        <v>46107.79872496528</v>
       </c>
       <c r="D37" s="8">
-        <v>46220.76588760417</v>
+        <v>46220.93255427083</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3634,13 +3634,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.4994959375</v>
+        <v>46073.66616260417</v>
       </c>
       <c r="C38" s="5">
-        <v>46107.63195207176</v>
+        <v>46107.79861873842</v>
       </c>
       <c r="D38" s="5">
-        <v>46107.63195350695</v>
+        <v>46107.798620173606</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3695,13 +3695,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.49949421296</v>
+        <v>46073.66616087963</v>
       </c>
       <c r="C39" s="8">
-        <v>46107.6320437963</v>
+        <v>46107.798710462965</v>
       </c>
       <c r="D39" s="8">
-        <v>46107.63204511574</v>
+        <v>46107.79871178241</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3756,13 +3756,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.499496018514</v>
+        <v>46073.666162685186</v>
       </c>
       <c r="C40" s="5">
-        <v>46098.51516494213</v>
+        <v>46098.681831608796</v>
       </c>
       <c r="D40" s="5">
-        <v>46098.51535857639</v>
+        <v>46098.682025243055</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3821,13 +3821,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.49949633102</v>
+        <v>46073.66616299769</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.36488233796</v>
+        <v>46097.531549004634</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.36488371528</v>
+        <v>46097.531550381944</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3882,13 +3882,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.49949665509</v>
+        <v>46073.66616332176</v>
       </c>
       <c r="C42" s="5">
-        <v>46098.51514953704</v>
+        <v>46098.68181620371</v>
       </c>
       <c r="D42" s="5">
-        <v>46098.51515129629</v>
+        <v>46098.68181796296</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3943,13 +3943,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.514133715275</v>
+        <v>46076.680800381946</v>
       </c>
       <c r="C43" s="8">
-        <v>46107.63418584491</v>
+        <v>46107.80085251157</v>
       </c>
       <c r="D43" s="8">
-        <v>46107.634225173606</v>
+        <v>46107.80089184028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4008,13 +4008,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.51685321759</v>
+        <v>46076.68351988426</v>
       </c>
       <c r="C44" s="5">
-        <v>46107.63219305556</v>
+        <v>46107.79885972222</v>
       </c>
       <c r="D44" s="5">
-        <v>46107.632194861115</v>
+        <v>46107.79886152778</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4073,13 +4073,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46076.5170812037</v>
+        <v>46076.68374787037</v>
       </c>
       <c r="C45" s="8">
-        <v>46107.634169467594</v>
+        <v>46107.80083613426</v>
       </c>
       <c r="D45" s="8">
-        <v>46107.63417105324</v>
+        <v>46107.80083771991</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4138,13 +4138,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46099.36346302083</v>
+        <v>46099.5301296875</v>
       </c>
       <c r="C46" s="5">
-        <v>46120.4972005787</v>
+        <v>46120.66386724537</v>
       </c>
       <c r="D46" s="5">
-        <v>46133.46426173611</v>
+        <v>46133.63092840278</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4203,13 +4203,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46099.36377777778</v>
+        <v>46099.53044444445</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.63450909722</v>
+        <v>46107.80117576389</v>
       </c>
       <c r="D47" s="8">
-        <v>46107.63451070602</v>
+        <v>46107.80117737269</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>100</v>
@@ -4258,13 +4258,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46099.36391869213</v>
+        <v>46099.53058535879</v>
       </c>
       <c r="C48" s="5">
-        <v>46120.49764869213</v>
+        <v>46120.664315358794</v>
       </c>
       <c r="D48" s="5">
-        <v>46120.49765023148</v>
+        <v>46120.664316898146</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>168</v>
@@ -4313,13 +4313,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46099.68312449074</v>
+        <v>46099.84979115741</v>
       </c>
       <c r="C49" s="8">
-        <v>46105.58778537037</v>
+        <v>46105.754452037036</v>
       </c>
       <c r="D49" s="8">
-        <v>46120.475501030094</v>
+        <v>46120.64216769676</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4368,13 +4368,13 @@
         <v>178</v>
       </c>
       <c r="B50" s="5">
-        <v>46099.683179837964</v>
+        <v>46099.84984650463</v>
       </c>
       <c r="C50" s="5">
-        <v>46120.49795726852</v>
+        <v>46120.66462393518</v>
       </c>
       <c r="D50" s="5">
-        <v>46120.49795851852</v>
+        <v>46120.664625185185</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>179</v>
@@ -4423,13 +4423,13 @@
         <v>180</v>
       </c>
       <c r="B51" s="8">
-        <v>46099.683643703705</v>
+        <v>46099.85031037037</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.497969131946</v>
+        <v>46120.66463579861</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.497970219905</v>
+        <v>46120.66463688658</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>181</v>
@@ -4478,13 +4478,13 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46099.364613391204</v>
+        <v>46099.53128005787</v>
       </c>
       <c r="C52" s="5">
-        <v>46120.47419332176</v>
+        <v>46120.64085998843</v>
       </c>
       <c r="D52" s="5">
-        <v>46120.497655694446</v>
+        <v>46120.66432236111</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -4533,13 +4533,13 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.49949696759</v>
+        <v>46073.66616363426</v>
       </c>
       <c r="C53" s="8">
-        <v>46171.53434295139</v>
+        <v>46171.70100961806</v>
       </c>
       <c r="D53" s="8">
-        <v>46171.53435428241</v>
+        <v>46171.70102094907</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>188</v>
@@ -4586,13 +4586,13 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.499497337965</v>
+        <v>46073.66616400463</v>
       </c>
       <c r="C54" s="5">
-        <v>46098.35444456019</v>
+        <v>46098.52111122685</v>
       </c>
       <c r="D54" s="5">
-        <v>46098.3544667824</v>
+        <v>46098.521133449074</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -4651,13 +4651,13 @@
         <v>195</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.49949548611</v>
+        <v>46073.666162152775</v>
       </c>
       <c r="C55" s="8">
-        <v>46114.62113092592</v>
+        <v>46114.787797592595</v>
       </c>
       <c r="D55" s="8">
-        <v>46114.621132534725</v>
+        <v>46114.78779920139</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>196</v>
@@ -4716,13 +4716,13 @@
         <v>199</v>
       </c>
       <c r="B56" s="5">
-        <v>46091.50057788195</v>
+        <v>46091.66724454861</v>
       </c>
       <c r="C56" s="5">
-        <v>46114.62123172454</v>
+        <v>46114.78789839121</v>
       </c>
       <c r="D56" s="5">
-        <v>46114.62124690972</v>
+        <v>46114.787913576394</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -4781,13 +4781,13 @@
         <v>202</v>
       </c>
       <c r="B57" s="8">
-        <v>46091.500609560186</v>
+        <v>46091.66727622686</v>
       </c>
       <c r="C57" s="8">
-        <v>46171.53432277778</v>
+        <v>46171.70098944445</v>
       </c>
       <c r="D57" s="8">
-        <v>46171.53434356481</v>
+        <v>46171.70101023148</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>203</v>
@@ -4846,13 +4846,13 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.49949594907</v>
+        <v>46073.666162615744</v>
       </c>
       <c r="C58" s="5">
-        <v>46105.53177052083</v>
+        <v>46105.6984371875</v>
       </c>
       <c r="D58" s="5">
-        <v>46105.53178506944</v>
+        <v>46105.69845173611</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -4899,13 +4899,13 @@
         <v>211</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.499496516204</v>
+        <v>46073.666163182876</v>
       </c>
       <c r="C59" s="8">
-        <v>46098.51852486111</v>
+        <v>46098.68519152778</v>
       </c>
       <c r="D59" s="8">
-        <v>46098.51854119213</v>
+        <v>46098.6852078588</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>212</v>
@@ -4964,13 +4964,13 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.49949688658</v>
+        <v>46073.66616355324</v>
       </c>
       <c r="C60" s="5">
-        <v>46105.53175085648</v>
+        <v>46105.69841752315</v>
       </c>
       <c r="D60" s="5">
-        <v>46105.595200752316</v>
+        <v>46105.76186741898</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5029,13 +5029,13 @@
         <v>219</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.499497233795</v>
+        <v>46073.66616390046</v>
       </c>
       <c r="C61" s="8">
-        <v>46128.602597476856</v>
+        <v>46128.76926414351</v>
       </c>
       <c r="D61" s="8">
-        <v>46128.602609062495</v>
+        <v>46128.769275729166</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>220</v>
@@ -5082,13 +5082,13 @@
         <v>222</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4994975463</v>
+        <v>46073.66616421296</v>
       </c>
       <c r="C62" s="5">
-        <v>46105.595783425924</v>
+        <v>46105.76245009259</v>
       </c>
       <c r="D62" s="5">
-        <v>46105.59579931713</v>
+        <v>46105.7624659838</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>223</v>
@@ -5147,13 +5147,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.49949862268</v>
+        <v>46073.66616528935</v>
       </c>
       <c r="C63" s="8">
-        <v>46128.326897719904</v>
+        <v>46128.493564386576</v>
       </c>
       <c r="D63" s="8">
-        <v>46128.603114791666</v>
+        <v>46128.76978145834</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>228</v>
@@ -5212,13 +5212,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.49949893518</v>
+        <v>46073.666165601855</v>
       </c>
       <c r="C64" s="5">
-        <v>46128.60258145833</v>
+        <v>46128.769248125</v>
       </c>
       <c r="D64" s="5">
-        <v>46128.60259846065</v>
+        <v>46128.76926512731</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5277,13 +5277,13 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.49949923611</v>
+        <v>46073.666165902774</v>
       </c>
       <c r="C65" s="8">
-        <v>46120.50273689815</v>
+        <v>46120.66940356481</v>
       </c>
       <c r="D65" s="8">
-        <v>46229.042533796295</v>
+        <v>46229.20920046297</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>209</v>
@@ -5330,13 +5330,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.49949353009</v>
+        <v>46073.666160196764</v>
       </c>
       <c r="C66" s="5">
-        <v>46113.65978219907</v>
+        <v>46113.826448865744</v>
       </c>
       <c r="D66" s="5">
-        <v>46121.0390146412</v>
+        <v>46121.20568130787</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5395,13 +5395,13 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.499493310184</v>
+        <v>46073.666159976856</v>
       </c>
       <c r="C67" s="8">
-        <v>46113.65980471065</v>
+        <v>46113.82647137731</v>
       </c>
       <c r="D67" s="8">
-        <v>46113.659806400465</v>
+        <v>46113.82647306713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5460,13 +5460,13 @@
         <v>242</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.49949299768</v>
+        <v>46073.66615966435</v>
       </c>
       <c r="C68" s="5">
-        <v>46120.50192715278</v>
+        <v>46120.66859381944</v>
       </c>
       <c r="D68" s="5">
-        <v>46120.50194306713</v>
+        <v>46120.668609733795</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>55</v>
@@ -5525,13 +5525,13 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.49949958333</v>
+        <v>46073.66616625</v>
       </c>
       <c r="C69" s="8">
-        <v>46120.502533032406</v>
+        <v>46120.66919969907</v>
       </c>
       <c r="D69" s="8">
-        <v>46120.50254931713</v>
+        <v>46120.6692159838</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5590,13 +5590,13 @@
         <v>246</v>
       </c>
       <c r="B70" s="5">
-        <v>46077.46202542824</v>
+        <v>46077.628692094906</v>
       </c>
       <c r="C70" s="5">
-        <v>46120.502574502316</v>
+        <v>46120.66924116898</v>
       </c>
       <c r="D70" s="5">
-        <v>46120.50258914352</v>
+        <v>46120.669255810186</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>247</v>
@@ -5655,13 +5655,13 @@
         <v>249</v>
       </c>
       <c r="B71" s="8">
-        <v>46099.376231111106</v>
+        <v>46099.54289777778</v>
       </c>
       <c r="C71" s="8">
-        <v>46126.68080083333</v>
+        <v>46126.8474675</v>
       </c>
       <c r="D71" s="8">
-        <v>46126.680802476854</v>
+        <v>46126.84746914352</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>250</v>
@@ -5718,13 +5718,13 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.49949376157</v>
+        <v>46073.66616042824</v>
       </c>
       <c r="C72" s="5">
-        <v>46161.743501944446</v>
+        <v>46161.91016861111</v>
       </c>
       <c r="D72" s="5">
-        <v>46222.40023796297</v>
+        <v>46222.566904629624</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5771,13 +5771,13 @@
         <v>255</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.49949402778</v>
+        <v>46073.66616069444</v>
       </c>
       <c r="C73" s="8">
-        <v>46133.46370634259</v>
+        <v>46133.63037300926</v>
       </c>
       <c r="D73" s="8">
-        <v>46223.65327248843</v>
+        <v>46223.81993915509</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>256</v>
@@ -5836,13 +5836,13 @@
         <v>258</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.49949425926</v>
+        <v>46073.666160925924</v>
       </c>
       <c r="C74" s="5">
-        <v>46133.46440752315</v>
+        <v>46133.63107418982</v>
       </c>
       <c r="D74" s="5">
-        <v>46223.65326883102</v>
+        <v>46223.81993549768</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>238</v>
@@ -5901,13 +5901,13 @@
         <v>261</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.49949450231</v>
+        <v>46073.66616116898</v>
       </c>
       <c r="C75" s="8">
-        <v>46133.46520177083</v>
+        <v>46133.6318684375</v>
       </c>
       <c r="D75" s="8">
-        <v>46223.65326532407</v>
+        <v>46223.81993199074</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>241</v>
@@ -5966,13 +5966,13 @@
         <v>264</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.49949475694</v>
+        <v>46073.66616142361</v>
       </c>
       <c r="C76" s="5">
-        <v>46148.27068769676</v>
+        <v>46148.43735436343</v>
       </c>
       <c r="D76" s="5">
-        <v>46223.65326097222</v>
+        <v>46223.81992763889</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>245</v>
@@ -6031,13 +6031,13 @@
         <v>266</v>
       </c>
       <c r="B77" s="8">
-        <v>46077.6559583912</v>
+        <v>46077.822625057874</v>
       </c>
       <c r="C77" s="8">
-        <v>46133.465182430555</v>
+        <v>46133.63184909722</v>
       </c>
       <c r="D77" s="8">
-        <v>46223.653257488426</v>
+        <v>46223.81992415509</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>248</v>
@@ -6096,13 +6096,13 @@
         <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.499494965276</v>
+        <v>46073.66616163195</v>
       </c>
       <c r="C78" s="5">
-        <v>46157.31385315972</v>
+        <v>46157.48051982639</v>
       </c>
       <c r="D78" s="5">
-        <v>46223.653252662036</v>
+        <v>46223.8199193287</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>206</v>
@@ -6161,13 +6161,13 @@
         <v>271</v>
       </c>
       <c r="B79" s="8">
-        <v>46073.49949519676</v>
+        <v>46073.666161863424</v>
       </c>
       <c r="C79" s="8">
-        <v>46161.74348398148</v>
+        <v>46161.91015064815</v>
       </c>
       <c r="D79" s="8">
-        <v>46223.65324719908</v>
+        <v>46223.81991386574</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>272</v>
@@ -6226,13 +6226,13 @@
         <v>274</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.49949351852</v>
+        <v>46073.66616018518</v>
       </c>
       <c r="C80" s="5">
-        <v>46174.49026890047</v>
+        <v>46174.65693556713</v>
       </c>
       <c r="D80" s="5">
-        <v>46174.49037211806</v>
+        <v>46174.65703878472</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>275</v>
@@ -6279,13 +6279,13 @@
         <v>277</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.499493877316</v>
+        <v>46073.66616054398</v>
       </c>
       <c r="C81" s="8">
-        <v>46161.74285855324</v>
+        <v>46161.909525219904</v>
       </c>
       <c r="D81" s="8">
-        <v>46174.49044193287</v>
+        <v>46174.65710859954</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>278</v>
@@ -6344,13 +6344,13 @@
         <v>280</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.499494143514</v>
+        <v>46073.666160810186</v>
       </c>
       <c r="C82" s="5">
-        <v>46161.74280395833</v>
+        <v>46161.909470625</v>
       </c>
       <c r="D82" s="5">
-        <v>46223.66722725694</v>
+        <v>46223.83389392361</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>251</v>
@@ -6409,13 +6409,13 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.499494421296</v>
+        <v>46073.66616108797</v>
       </c>
       <c r="C83" s="8">
-        <v>46142.7623125463</v>
+        <v>46142.928979212964</v>
       </c>
       <c r="D83" s="8">
-        <v>46174.490442951384</v>
+        <v>46174.657109618056</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>284</v>
@@ -6474,13 +6474,13 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.499494675925</v>
+        <v>46073.6661613426</v>
       </c>
       <c r="C84" s="5">
-        <v>46174.490250069444</v>
+        <v>46174.656916736116</v>
       </c>
       <c r="D84" s="5">
-        <v>46240.548141458334</v>
+        <v>46240.714808125005</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6539,13 +6539,13 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46073.49949494213</v>
+        <v>46073.666161608795</v>
       </c>
       <c r="C85" s="8">
-        <v>46232.498578680556</v>
+        <v>46232.66524534722</v>
       </c>
       <c r="D85" s="8">
-        <v>46232.49859103009</v>
+        <v>46232.66525769676</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6594,13 +6594,13 @@
         <v>292</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.49949523148</v>
+        <v>46073.666161898145</v>
       </c>
       <c r="C86" s="5">
-        <v>46232.49855480324</v>
+        <v>46232.665221469906</v>
       </c>
       <c r="D86" s="5">
-        <v>46232.498571018514</v>
+        <v>46232.665237685185</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>293</v>
@@ -6659,13 +6659,13 @@
         <v>296</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.49949556713</v>
+        <v>46073.6661622338</v>
       </c>
       <c r="C87" s="8">
-        <v>46232.498561875</v>
+        <v>46232.665228541664</v>
       </c>
       <c r="D87" s="8">
-        <v>46232.49857969907</v>
+        <v>46232.66524636574</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>297</v>
